--- a/data/numeric/input/old_data_89/系统中工维条线人员持证情况_已脱敏.xlsx
+++ b/data/numeric/input/old_data_89/系统中工维条线人员持证情况_已脱敏.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\panzheng1\Documents\work\files\tmp\20260205\graph_data\输入数据\old_data_89\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905639E5-4E0F-47B1-96A0-06131DA7F619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="14725"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="职业技能" sheetId="1" r:id="rId1"/>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="728">
   <si>
     <t>一、填写说明：
 1. 不允许删除列、隐藏列；不允许填写公式，必须采用粘贴数值的形式；
@@ -220,9 +226,6 @@
     <t>20-中级</t>
   </si>
   <si>
-    <t>中华人民共和国人力资源和社会保障部、工业和信息化部</t>
-  </si>
-  <si>
     <t>Aid_9</t>
   </si>
   <si>
@@ -542,9 +545,6 @@
   </si>
   <si>
     <t>A公司33</t>
-  </si>
-  <si>
-    <t>联通时科传媒有限公司</t>
   </si>
   <si>
     <t>Aid_34</t>
@@ -1069,9 +1069,6 @@
     <t>B公司34</t>
   </si>
   <si>
-    <t>飞利信信息有限公司</t>
-  </si>
-  <si>
     <t>Bid35</t>
   </si>
   <si>
@@ -1141,12 +1138,6 @@
 2. D-删除：代表删除当前记录。</t>
   </si>
   <si>
-    <t>孙萍</t>
-  </si>
-  <si>
-    <t>李艳</t>
-  </si>
-  <si>
     <t>顺序</t>
   </si>
   <si>
@@ -1183,21 +1174,6 @@
     <t>聘任情况</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>E0023070187</t>
-  </si>
-  <si>
-    <t>E0023070188</t>
-  </si>
-  <si>
-    <t>白圣梅</t>
-  </si>
-  <si>
-    <t>新宇龙信息科技有限公司</t>
-  </si>
-  <si>
     <t>网络运维管理</t>
   </si>
   <si>
@@ -1216,246 +1192,33 @@
     <t>10-考试</t>
   </si>
   <si>
-    <t>1722329820</t>
-  </si>
-  <si>
     <t>SELF-自助门户</t>
   </si>
   <si>
     <t>Y-是</t>
   </si>
   <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>张淑英</t>
-  </si>
-  <si>
-    <t>包秋忠</t>
-  </si>
-  <si>
-    <t>维涛信息有限公司</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>903</t>
-  </si>
-  <si>
-    <t>邓萍</t>
-  </si>
-  <si>
-    <t>包文路</t>
-  </si>
-  <si>
-    <t>陈洋</t>
-  </si>
-  <si>
-    <t>1597</t>
-  </si>
-  <si>
-    <t>张荣</t>
-  </si>
-  <si>
-    <t>江杰</t>
-  </si>
-  <si>
-    <t>联软网络有限公司</t>
-  </si>
-  <si>
-    <t>张婷</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>E0023070371</t>
-  </si>
-  <si>
-    <t>E0023070372</t>
-  </si>
-  <si>
-    <t>刘帆</t>
-  </si>
-  <si>
-    <t>许旭</t>
-  </si>
-  <si>
     <t>业务与系统支撑</t>
   </si>
   <si>
-    <t>曹玉英</t>
-  </si>
-  <si>
     <t>2023-10-14</t>
   </si>
   <si>
-    <t>人力资源和社会保障部、工业和信息化部</t>
-  </si>
-  <si>
     <t>CORE-人事核心</t>
   </si>
   <si>
-    <t>1461</t>
-  </si>
-  <si>
-    <t>沙杨</t>
-  </si>
-  <si>
-    <t>晁望童</t>
-  </si>
-  <si>
-    <t>鑫博腾飞传媒有限公司</t>
-  </si>
-  <si>
-    <t>263</t>
-  </si>
-  <si>
-    <t>E0023070445</t>
-  </si>
-  <si>
-    <t>何洋</t>
-  </si>
-  <si>
-    <t>网新恒天传媒有限公司</t>
-  </si>
-  <si>
-    <t>刘兵</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>E0023077793</t>
-  </si>
-  <si>
-    <t>泰麒麟传媒有限公司</t>
-  </si>
-  <si>
-    <t>陶春梅</t>
-  </si>
-  <si>
-    <t>865</t>
-  </si>
-  <si>
-    <t>E0023077020</t>
-  </si>
-  <si>
-    <t>王玉</t>
-  </si>
-  <si>
-    <t>维旺明信息有限公司</t>
-  </si>
-  <si>
-    <t>孙琴</t>
-  </si>
-  <si>
-    <t>1424</t>
-  </si>
-  <si>
-    <t>E1000042163</t>
-  </si>
-  <si>
-    <t>陈利</t>
-  </si>
-  <si>
-    <t>惠派国际公司网络有限公司</t>
-  </si>
-  <si>
-    <t>张超</t>
-  </si>
-  <si>
     <t>2022-11-26</t>
   </si>
   <si>
-    <t>31320221032032300127</t>
-  </si>
-  <si>
-    <t>1396</t>
-  </si>
-  <si>
-    <t>柴洁</t>
-  </si>
-  <si>
-    <t>侯淑兰</t>
-  </si>
-  <si>
-    <t>巨奥网络有限公司</t>
-  </si>
-  <si>
-    <t>王璐</t>
-  </si>
-  <si>
-    <t>1603</t>
-  </si>
-  <si>
-    <t>E1000102403</t>
-  </si>
-  <si>
-    <t>E1000102404</t>
-  </si>
-  <si>
-    <t>李林</t>
-  </si>
-  <si>
-    <t>天益信息有限公司</t>
-  </si>
-  <si>
-    <t>谢雪梅</t>
-  </si>
-  <si>
-    <t>781</t>
-  </si>
-  <si>
-    <t>李亮</t>
-  </si>
-  <si>
-    <t>王帆</t>
-  </si>
-  <si>
-    <t>开发区世创网络有限公司</t>
-  </si>
-  <si>
     <t>无线网优化</t>
   </si>
   <si>
-    <t>赵淑珍</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>E0023070102</t>
-  </si>
-  <si>
-    <t>徐丽丽</t>
-  </si>
-  <si>
-    <t>群英科技有限公司</t>
-  </si>
-  <si>
-    <t>王建军</t>
-  </si>
-  <si>
     <t>2003-09-01</t>
   </si>
   <si>
-    <t>通信行业</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>郑秀华</t>
-  </si>
-  <si>
-    <t>昂歌信息信息有限公司</t>
-  </si>
-  <si>
-    <t>赵艳</t>
-  </si>
-  <si>
     <t>1998-08-01</t>
   </si>
   <si>
@@ -1465,399 +1228,42 @@
     <t>105-助理工程师-GC-工程技术人员</t>
   </si>
   <si>
-    <t>徐州邮电局</t>
-  </si>
-  <si>
-    <t>963</t>
-  </si>
-  <si>
-    <t>E0023077630</t>
-  </si>
-  <si>
-    <t>程曦</t>
-  </si>
-  <si>
-    <t>诺依曼软件传媒有限公司</t>
-  </si>
-  <si>
-    <t>974</t>
-  </si>
-  <si>
-    <t>E0023077674</t>
-  </si>
-  <si>
-    <t>宾洁</t>
-  </si>
-  <si>
-    <t>图龙信息网络有限公司</t>
-  </si>
-  <si>
-    <t>姜燕</t>
-  </si>
-  <si>
-    <t>893</t>
-  </si>
-  <si>
-    <t>李红霞</t>
-  </si>
-  <si>
-    <t>单晓芳</t>
-  </si>
-  <si>
-    <t>天开科技有限公司</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>李娜</t>
-  </si>
-  <si>
-    <t>陈燕</t>
-  </si>
-  <si>
-    <t>诺依曼软件网络有限公司</t>
-  </si>
-  <si>
-    <t>程涛</t>
-  </si>
-  <si>
-    <t>1065</t>
-  </si>
-  <si>
-    <t>马兵</t>
-  </si>
-  <si>
-    <t>高彬</t>
-  </si>
-  <si>
-    <t>信诚致远信息有限公司</t>
-  </si>
-  <si>
-    <t>程颖</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>吴倩</t>
-  </si>
-  <si>
-    <t>董波</t>
-  </si>
-  <si>
-    <t>海创信息有限公司</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>高东</t>
-  </si>
-  <si>
-    <t>窦霖</t>
-  </si>
-  <si>
-    <t>济南亿次元信息有限公司</t>
-  </si>
-  <si>
     <t>2020-10-17</t>
   </si>
   <si>
-    <t>中华人民共和国人力资源和社会保障部、中华人民共和国工业和信息</t>
-  </si>
-  <si>
-    <t>31320201032032200264</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>刘雪梅</t>
-  </si>
-  <si>
-    <t>程凤英</t>
-  </si>
-  <si>
-    <t>襄樊地球村网络有限公司</t>
-  </si>
-  <si>
-    <t>叶娟</t>
-  </si>
-  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>信息产业部</t>
-  </si>
-  <si>
-    <t>0710335511</t>
-  </si>
-  <si>
     <t>N-否</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>丁静</t>
-  </si>
-  <si>
-    <t>程楠</t>
-  </si>
-  <si>
-    <t>网新恒天网络有限公司</t>
-  </si>
-  <si>
-    <t>徐凤英</t>
-  </si>
-  <si>
     <t>1995-09-01</t>
   </si>
   <si>
     <t>20-企业内部评定</t>
   </si>
   <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>陈秀华</t>
-  </si>
-  <si>
-    <t>杜强</t>
-  </si>
-  <si>
-    <t>商软冠联科技有限公司</t>
-  </si>
-  <si>
-    <t>数字100网络有限公司</t>
-  </si>
-  <si>
     <t>2011-08-29</t>
   </si>
   <si>
-    <t>江苏省人力资源和社会保障厅</t>
-  </si>
-  <si>
-    <t>10577572071</t>
-  </si>
-  <si>
-    <t>1075</t>
-  </si>
-  <si>
-    <t>张丽</t>
-  </si>
-  <si>
-    <t>合联电子科技有限公司</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>赵琴</t>
-  </si>
-  <si>
-    <t>段煜</t>
-  </si>
-  <si>
-    <t>国讯传媒有限公司</t>
-  </si>
-  <si>
-    <t>1248</t>
-  </si>
-  <si>
-    <t>潘静</t>
-  </si>
-  <si>
-    <t>范彬</t>
-  </si>
-  <si>
-    <t>艾提科信信息有限公司</t>
-  </si>
-  <si>
-    <t>1249</t>
-  </si>
-  <si>
-    <t>仝平</t>
-  </si>
-  <si>
-    <t>晖来计算机传媒有限公司</t>
-  </si>
-  <si>
     <t>2011-12-31</t>
   </si>
   <si>
-    <t>1110406681</t>
-  </si>
-  <si>
     <t>交换技术（中级）</t>
   </si>
   <si>
-    <t>1250</t>
-  </si>
-  <si>
-    <t>杨亮</t>
-  </si>
-  <si>
-    <t>黄石金承网络有限公司</t>
-  </si>
-  <si>
-    <t>31320221032032500136</t>
-  </si>
-  <si>
     <t>传输与接入（中级）</t>
   </si>
   <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>E0023070448</t>
-  </si>
-  <si>
-    <t>E0023070449</t>
-  </si>
-  <si>
-    <t>陈宇</t>
-  </si>
-  <si>
-    <t>思优科技有限公司</t>
-  </si>
-  <si>
-    <t>甘俊</t>
-  </si>
-  <si>
-    <t>31320221032032400259</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>郑坤</t>
-  </si>
-  <si>
-    <t>付锦</t>
-  </si>
-  <si>
-    <t>毕博诚科技有限公司</t>
-  </si>
-  <si>
-    <t>1167</t>
-  </si>
-  <si>
-    <t>赵桂英</t>
-  </si>
-  <si>
-    <t>李红</t>
-  </si>
-  <si>
-    <t>济南亿次元传媒有限公司</t>
-  </si>
-  <si>
-    <t>高勇</t>
-  </si>
-  <si>
-    <t>1526</t>
-  </si>
-  <si>
-    <t>E1000088245</t>
-  </si>
-  <si>
-    <t>E1000088246</t>
-  </si>
-  <si>
-    <t>高晓娜</t>
-  </si>
-  <si>
-    <t>戴硕电子传媒有限公司</t>
-  </si>
-  <si>
     <t>动力运行维护</t>
   </si>
   <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>林琴</t>
-  </si>
-  <si>
-    <t>高玉</t>
-  </si>
-  <si>
-    <t>惠派国际公司信息有限公司</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>黄娟</t>
-  </si>
-  <si>
-    <t>龚鹏</t>
-  </si>
-  <si>
-    <t>国讯信息有限公司</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>E0023070784</t>
-  </si>
-  <si>
-    <t>E0023070785</t>
-  </si>
-  <si>
-    <t>夏冬梅</t>
-  </si>
-  <si>
-    <t>易动力网络有限公司</t>
-  </si>
-  <si>
     <t>无线网运行维护</t>
   </si>
   <si>
-    <t>陈林</t>
-  </si>
-  <si>
-    <t>1491</t>
-  </si>
-  <si>
-    <t>刘洁</t>
-  </si>
-  <si>
-    <t>郑雪</t>
-  </si>
-  <si>
-    <t>佳禾科技有限公司</t>
-  </si>
-  <si>
-    <t>张玉华</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>E0023070427</t>
-  </si>
-  <si>
-    <t>E0023070428</t>
-  </si>
-  <si>
-    <t>王龙</t>
-  </si>
-  <si>
-    <t>易莉</t>
-  </si>
-  <si>
     <t>2011-12-30</t>
   </si>
   <si>
-    <t>MBP软件传媒有限公司</t>
-  </si>
-  <si>
-    <t>1110405953</t>
-  </si>
-  <si>
     <t>KX-科学研究人员</t>
   </si>
   <si>
@@ -2192,373 +1598,684 @@
   </si>
   <si>
     <t>occ41</t>
+  </si>
+  <si>
+    <t>num1</t>
+  </si>
+  <si>
+    <t>num2</t>
+  </si>
+  <si>
+    <t>num3</t>
+  </si>
+  <si>
+    <t>num4</t>
+  </si>
+  <si>
+    <t>num5</t>
+  </si>
+  <si>
+    <t>num6</t>
+  </si>
+  <si>
+    <t>num7</t>
+  </si>
+  <si>
+    <t>num8</t>
+  </si>
+  <si>
+    <t>num9</t>
+  </si>
+  <si>
+    <t>num10</t>
+  </si>
+  <si>
+    <t>num11</t>
+  </si>
+  <si>
+    <t>num12</t>
+  </si>
+  <si>
+    <t>num13</t>
+  </si>
+  <si>
+    <t>num14</t>
+  </si>
+  <si>
+    <t>num15</t>
+  </si>
+  <si>
+    <t>num16</t>
+  </si>
+  <si>
+    <t>num17</t>
+  </si>
+  <si>
+    <t>num18</t>
+  </si>
+  <si>
+    <t>num19</t>
+  </si>
+  <si>
+    <t>num20</t>
+  </si>
+  <si>
+    <t>num21</t>
+  </si>
+  <si>
+    <t>num22</t>
+  </si>
+  <si>
+    <t>num23</t>
+  </si>
+  <si>
+    <t>num24</t>
+  </si>
+  <si>
+    <t>num25</t>
+  </si>
+  <si>
+    <t>num26</t>
+  </si>
+  <si>
+    <t>num27</t>
+  </si>
+  <si>
+    <t>num28</t>
+  </si>
+  <si>
+    <t>num29</t>
+  </si>
+  <si>
+    <t>num30</t>
+  </si>
+  <si>
+    <t>num31</t>
+  </si>
+  <si>
+    <t>num32</t>
+  </si>
+  <si>
+    <t>num33</t>
+  </si>
+  <si>
+    <t>num34</t>
+  </si>
+  <si>
+    <t>num35</t>
+  </si>
+  <si>
+    <t>num36</t>
+  </si>
+  <si>
+    <t>num37</t>
+  </si>
+  <si>
+    <t>num38</t>
+  </si>
+  <si>
+    <t>num39</t>
+  </si>
+  <si>
+    <t>C人员1</t>
+  </si>
+  <si>
+    <t>C人员2</t>
+  </si>
+  <si>
+    <t>C人员3</t>
+  </si>
+  <si>
+    <t>C人员4</t>
+  </si>
+  <si>
+    <t>C人员5</t>
+  </si>
+  <si>
+    <t>C人员6</t>
+  </si>
+  <si>
+    <t>C人员7</t>
+  </si>
+  <si>
+    <t>C人员8</t>
+  </si>
+  <si>
+    <t>C人员9</t>
+  </si>
+  <si>
+    <t>C人员10</t>
+  </si>
+  <si>
+    <t>C人员11</t>
+  </si>
+  <si>
+    <t>C人员12</t>
+  </si>
+  <si>
+    <t>C人员13</t>
+  </si>
+  <si>
+    <t>C人员14</t>
+  </si>
+  <si>
+    <t>C人员15</t>
+  </si>
+  <si>
+    <t>C人员16</t>
+  </si>
+  <si>
+    <t>C人员17</t>
+  </si>
+  <si>
+    <t>C人员18</t>
+  </si>
+  <si>
+    <t>C人员19</t>
+  </si>
+  <si>
+    <t>C人员20</t>
+  </si>
+  <si>
+    <t>C人员21</t>
+  </si>
+  <si>
+    <t>C人员22</t>
+  </si>
+  <si>
+    <t>C人员23</t>
+  </si>
+  <si>
+    <t>C人员24</t>
+  </si>
+  <si>
+    <t>C人员25</t>
+  </si>
+  <si>
+    <t>C人员26</t>
+  </si>
+  <si>
+    <t>C人员27</t>
+  </si>
+  <si>
+    <t>C人员28</t>
+  </si>
+  <si>
+    <t>C人员29</t>
+  </si>
+  <si>
+    <t>C人员30</t>
+  </si>
+  <si>
+    <t>C人员31</t>
+  </si>
+  <si>
+    <t>C人员32</t>
+  </si>
+  <si>
+    <t>C人员33</t>
+  </si>
+  <si>
+    <t>C人员34</t>
+  </si>
+  <si>
+    <t>C人员35</t>
+  </si>
+  <si>
+    <t>C人员36</t>
+  </si>
+  <si>
+    <t>C人员37</t>
+  </si>
+  <si>
+    <t>C人员38</t>
+  </si>
+  <si>
+    <t>C人员39</t>
+  </si>
+  <si>
+    <t>C人员40</t>
+  </si>
+  <si>
+    <t>D人员1</t>
+  </si>
+  <si>
+    <t>D人员2</t>
+  </si>
+  <si>
+    <t>D人员3</t>
+  </si>
+  <si>
+    <t>D人员4</t>
+  </si>
+  <si>
+    <t>D人员5</t>
+  </si>
+  <si>
+    <t>D人员6</t>
+  </si>
+  <si>
+    <t>D人员7</t>
+  </si>
+  <si>
+    <t>D人员8</t>
+  </si>
+  <si>
+    <t>D人员9</t>
+  </si>
+  <si>
+    <t>D人员10</t>
+  </si>
+  <si>
+    <t>D人员11</t>
+  </si>
+  <si>
+    <t>D人员12</t>
+  </si>
+  <si>
+    <t>D人员13</t>
+  </si>
+  <si>
+    <t>D人员14</t>
+  </si>
+  <si>
+    <t>D人员15</t>
+  </si>
+  <si>
+    <t>D人员16</t>
+  </si>
+  <si>
+    <t>D人员17</t>
+  </si>
+  <si>
+    <t>D人员18</t>
+  </si>
+  <si>
+    <t>D人员19</t>
+  </si>
+  <si>
+    <t>D人员20</t>
+  </si>
+  <si>
+    <t>D人员21</t>
+  </si>
+  <si>
+    <t>D人员22</t>
+  </si>
+  <si>
+    <t>D人员23</t>
+  </si>
+  <si>
+    <t>D人员24</t>
+  </si>
+  <si>
+    <t>D人员25</t>
+  </si>
+  <si>
+    <t>D人员26</t>
+  </si>
+  <si>
+    <t>D人员27</t>
+  </si>
+  <si>
+    <t>D人员28</t>
+  </si>
+  <si>
+    <t>D人员29</t>
+  </si>
+  <si>
+    <t>D人员30</t>
+  </si>
+  <si>
+    <t>D人员31</t>
+  </si>
+  <si>
+    <t>D人员32</t>
+  </si>
+  <si>
+    <t>D人员33</t>
+  </si>
+  <si>
+    <t>D人员34</t>
+  </si>
+  <si>
+    <t>D人员35</t>
+  </si>
+  <si>
+    <t>D人员36</t>
+  </si>
+  <si>
+    <t>D人员37</t>
+  </si>
+  <si>
+    <t>D人员38</t>
+  </si>
+  <si>
+    <t>D人员39</t>
+  </si>
+  <si>
+    <t>D人员40</t>
+  </si>
+  <si>
+    <t>E公司1</t>
+  </si>
+  <si>
+    <t>E公司2</t>
+  </si>
+  <si>
+    <t>E公司3</t>
+  </si>
+  <si>
+    <t>E公司4</t>
+  </si>
+  <si>
+    <t>E公司5</t>
+  </si>
+  <si>
+    <t>E公司6</t>
+  </si>
+  <si>
+    <t>E公司7</t>
+  </si>
+  <si>
+    <t>E公司8</t>
+  </si>
+  <si>
+    <t>E公司9</t>
+  </si>
+  <si>
+    <t>E公司10</t>
+  </si>
+  <si>
+    <t>E公司11</t>
+  </si>
+  <si>
+    <t>E公司12</t>
+  </si>
+  <si>
+    <t>E公司13</t>
+  </si>
+  <si>
+    <t>E公司14</t>
+  </si>
+  <si>
+    <t>E公司15</t>
+  </si>
+  <si>
+    <t>E公司16</t>
+  </si>
+  <si>
+    <t>E公司17</t>
+  </si>
+  <si>
+    <t>E公司18</t>
+  </si>
+  <si>
+    <t>E公司19</t>
+  </si>
+  <si>
+    <t>E公司20</t>
+  </si>
+  <si>
+    <t>E公司21</t>
+  </si>
+  <si>
+    <t>E公司22</t>
+  </si>
+  <si>
+    <t>E公司23</t>
+  </si>
+  <si>
+    <t>E公司24</t>
+  </si>
+  <si>
+    <t>E公司25</t>
+  </si>
+  <si>
+    <t>E公司26</t>
+  </si>
+  <si>
+    <t>E公司27</t>
+  </si>
+  <si>
+    <t>E公司28</t>
+  </si>
+  <si>
+    <t>E公司29</t>
+  </si>
+  <si>
+    <t>E公司30</t>
+  </si>
+  <si>
+    <t>E公司31</t>
+  </si>
+  <si>
+    <t>E公司32</t>
+  </si>
+  <si>
+    <t>E公司33</t>
+  </si>
+  <si>
+    <t>E公司34</t>
+  </si>
+  <si>
+    <t>E公司35</t>
+  </si>
+  <si>
+    <t>E公司36</t>
+  </si>
+  <si>
+    <t>E公司37</t>
+  </si>
+  <si>
+    <t>E公司38</t>
+  </si>
+  <si>
+    <t>E公司39</t>
+  </si>
+  <si>
+    <t>F人员1</t>
+  </si>
+  <si>
+    <t>F人员2</t>
+  </si>
+  <si>
+    <t>F人员3</t>
+  </si>
+  <si>
+    <t>F人员4</t>
+  </si>
+  <si>
+    <t>F人员5</t>
+  </si>
+  <si>
+    <t>F人员6</t>
+  </si>
+  <si>
+    <t>F人员7</t>
+  </si>
+  <si>
+    <t>F人员8</t>
+  </si>
+  <si>
+    <t>F人员9</t>
+  </si>
+  <si>
+    <t>F人员10</t>
+  </si>
+  <si>
+    <t>F人员11</t>
+  </si>
+  <si>
+    <t>F人员12</t>
+  </si>
+  <si>
+    <t>F人员13</t>
+  </si>
+  <si>
+    <t>F人员14</t>
+  </si>
+  <si>
+    <t>F人员15</t>
+  </si>
+  <si>
+    <t>F人员16</t>
+  </si>
+  <si>
+    <t>F人员17</t>
+  </si>
+  <si>
+    <t>F人员18</t>
+  </si>
+  <si>
+    <t>F人员19</t>
+  </si>
+  <si>
+    <t>F人员20</t>
+  </si>
+  <si>
+    <t>F人员21</t>
+  </si>
+  <si>
+    <t>F人员22</t>
+  </si>
+  <si>
+    <t>F人员23</t>
+  </si>
+  <si>
+    <t>F人员24</t>
+  </si>
+  <si>
+    <t>F人员25</t>
+  </si>
+  <si>
+    <t>F人员26</t>
+  </si>
+  <si>
+    <t>F人员27</t>
+  </si>
+  <si>
+    <t>F人员28</t>
+  </si>
+  <si>
+    <t>F人员29</t>
+  </si>
+  <si>
+    <t>F人员30</t>
+  </si>
+  <si>
+    <t>F人员31</t>
+  </si>
+  <si>
+    <t>F人员32</t>
+  </si>
+  <si>
+    <t>F人员33</t>
+  </si>
+  <si>
+    <t>F人员34</t>
+  </si>
+  <si>
+    <t>F人员35</t>
+  </si>
+  <si>
+    <t>F人员36</t>
+  </si>
+  <si>
+    <t>F人员37</t>
+  </si>
+  <si>
+    <t>F人员38</t>
+  </si>
+  <si>
+    <t>F人员39</t>
+  </si>
+  <si>
+    <t>seq1</t>
+  </si>
+  <si>
+    <t>seq2</t>
+  </si>
+  <si>
+    <t>seq3</t>
+  </si>
+  <si>
+    <t>seq4</t>
+  </si>
+  <si>
+    <t>seq5</t>
+  </si>
+  <si>
+    <t>seq7</t>
+  </si>
+  <si>
+    <t>seq8</t>
+  </si>
+  <si>
+    <t>seq6</t>
+  </si>
+  <si>
+    <t>seq9</t>
+  </si>
+  <si>
+    <t>G公司1</t>
+  </si>
+  <si>
+    <t>G公司2</t>
+  </si>
+  <si>
+    <t>T公司</t>
+  </si>
+  <si>
+    <t>U公司</t>
+  </si>
+  <si>
+    <t>单位1</t>
+  </si>
+  <si>
+    <t>单位2</t>
+  </si>
+  <si>
+    <t>单位3</t>
+  </si>
+  <si>
+    <t>单位4</t>
+  </si>
+  <si>
+    <t>单位5</t>
+  </si>
+  <si>
+    <t>单位6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2566,310 +2283,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3154,17 +2585,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P41"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="5" max="5" width="11.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.5495495495495"/>
+    <col min="5" max="5" width="11.6328125" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3391,21 +2822,21 @@
         <v>58</v>
       </c>
       <c r="L10" t="s">
-        <v>59</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
         <v>60</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>61</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
       </c>
       <c r="F11" t="s">
         <v>42</v>
@@ -3416,16 +2847,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
         <v>64</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>65</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>66</v>
-      </c>
-      <c r="E12" t="s">
-        <v>67</v>
       </c>
       <c r="F12" t="s">
         <v>47</v>
@@ -3436,16 +2867,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
         <v>68</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>69</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>70</v>
-      </c>
-      <c r="E13" t="s">
-        <v>71</v>
       </c>
       <c r="F13" t="s">
         <v>32</v>
@@ -3456,16 +2887,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
         <v>72</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>73</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>74</v>
-      </c>
-      <c r="E14" t="s">
-        <v>75</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
@@ -3476,16 +2907,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
         <v>76</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>77</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>78</v>
-      </c>
-      <c r="E15" t="s">
-        <v>79</v>
       </c>
       <c r="F15" t="s">
         <v>47</v>
@@ -3496,16 +2927,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
         <v>80</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>81</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>82</v>
-      </c>
-      <c r="E16" t="s">
-        <v>83</v>
       </c>
       <c r="F16" t="s">
         <v>56</v>
@@ -3516,19 +2947,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
         <v>84</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>85</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>86</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>87</v>
-      </c>
-      <c r="F17" t="s">
-        <v>88</v>
       </c>
       <c r="G17" t="s">
         <v>22</v>
@@ -3536,19 +2967,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
         <v>89</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>90</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>91</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>92</v>
-      </c>
-      <c r="F18" t="s">
-        <v>93</v>
       </c>
       <c r="G18" t="s">
         <v>22</v>
@@ -3556,19 +2987,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
         <v>94</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>95</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>96</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>97</v>
-      </c>
-      <c r="F19" t="s">
-        <v>98</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
@@ -3576,19 +3007,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
         <v>99</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>100</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>101</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>102</v>
-      </c>
-      <c r="F20" t="s">
-        <v>103</v>
       </c>
       <c r="G20" t="s">
         <v>22</v>
@@ -3596,19 +3027,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" t="s">
         <v>104</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>105</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>106</v>
       </c>
-      <c r="E21" t="s">
-        <v>107</v>
-      </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
         <v>22</v>
@@ -3616,19 +3047,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
         <v>108</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>109</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>110</v>
       </c>
-      <c r="E22" t="s">
-        <v>111</v>
-      </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
         <v>22</v>
@@ -3636,19 +3067,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
         <v>112</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>113</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>114</v>
       </c>
-      <c r="E23" t="s">
-        <v>115</v>
-      </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s">
         <v>22</v>
@@ -3656,16 +3087,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
         <v>116</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>117</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>119</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -3676,19 +3107,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" t="s">
         <v>120</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>121</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>122</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>123</v>
-      </c>
-      <c r="F25" t="s">
-        <v>124</v>
       </c>
       <c r="G25" t="s">
         <v>22</v>
@@ -3696,16 +3127,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" t="s">
         <v>125</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>126</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>127</v>
-      </c>
-      <c r="E26" t="s">
-        <v>128</v>
       </c>
       <c r="F26" t="s">
         <v>47</v>
@@ -3716,19 +3147,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" t="s">
         <v>129</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>130</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>131</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>132</v>
-      </c>
-      <c r="F27" t="s">
-        <v>133</v>
       </c>
       <c r="G27" t="s">
         <v>22</v>
@@ -3736,19 +3167,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" t="s">
         <v>134</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>135</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>136</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>137</v>
-      </c>
-      <c r="F28" t="s">
-        <v>138</v>
       </c>
       <c r="G28" t="s">
         <v>22</v>
@@ -3756,19 +3187,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" t="s">
         <v>139</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>140</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>141</v>
       </c>
-      <c r="E29" t="s">
-        <v>142</v>
-      </c>
       <c r="F29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G29" t="s">
         <v>22</v>
@@ -3776,16 +3207,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" t="s">
         <v>143</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>144</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>145</v>
-      </c>
-      <c r="E30" t="s">
-        <v>146</v>
       </c>
       <c r="F30" t="s">
         <v>47</v>
@@ -3796,19 +3227,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" t="s">
         <v>147</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>148</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>149</v>
       </c>
-      <c r="E31" t="s">
-        <v>150</v>
-      </c>
       <c r="F31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s">
         <v>22</v>
@@ -3816,19 +3247,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" t="s">
         <v>151</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>152</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>153</v>
       </c>
-      <c r="E32" t="s">
-        <v>154</v>
-      </c>
       <c r="F32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s">
         <v>22</v>
@@ -3836,16 +3267,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" t="s">
         <v>155</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>156</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>157</v>
-      </c>
-      <c r="E33" t="s">
-        <v>158</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -3856,16 +3287,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" t="s">
         <v>159</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>160</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>161</v>
-      </c>
-      <c r="E34" t="s">
-        <v>162</v>
       </c>
       <c r="F34" t="s">
         <v>27</v>
@@ -3876,19 +3307,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" t="s">
         <v>163</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>164</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>165</v>
       </c>
-      <c r="E35" t="s">
-        <v>166</v>
-      </c>
       <c r="F35" t="s">
-        <v>167</v>
+        <v>720</v>
       </c>
       <c r="G35" t="s">
         <v>22</v>
@@ -3896,19 +3327,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" t="s">
         <v>168</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E36" t="s">
         <v>169</v>
       </c>
-      <c r="D36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E36" t="s">
-        <v>171</v>
-      </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G36" t="s">
         <v>22</v>
@@ -3916,16 +3347,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" t="s">
         <v>172</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E37" t="s">
         <v>173</v>
-      </c>
-      <c r="D37" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" t="s">
-        <v>175</v>
       </c>
       <c r="F37" t="s">
         <v>47</v>
@@ -3936,19 +3367,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
+        <v>174</v>
+      </c>
+      <c r="C38" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" t="s">
         <v>176</v>
       </c>
-      <c r="C38" t="s">
+      <c r="E38" t="s">
         <v>177</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>178</v>
-      </c>
-      <c r="E38" t="s">
-        <v>179</v>
-      </c>
-      <c r="F38" t="s">
-        <v>180</v>
       </c>
       <c r="G38" t="s">
         <v>22</v>
@@ -3956,16 +3387,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C39" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" t="s">
         <v>181</v>
       </c>
-      <c r="C39" t="s">
+      <c r="E39" t="s">
         <v>182</v>
-      </c>
-      <c r="D39" t="s">
-        <v>183</v>
-      </c>
-      <c r="E39" t="s">
-        <v>184</v>
       </c>
       <c r="F39" t="s">
         <v>27</v>
@@ -3976,19 +3407,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" t="s">
         <v>185</v>
       </c>
-      <c r="C40" t="s">
+      <c r="E40" t="s">
         <v>186</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>187</v>
-      </c>
-      <c r="E40" t="s">
-        <v>188</v>
-      </c>
-      <c r="F40" t="s">
-        <v>189</v>
       </c>
       <c r="G40" t="s">
         <v>22</v>
@@ -3996,19 +3427,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" t="s">
         <v>190</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>191</v>
       </c>
-      <c r="D41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E41" t="s">
-        <v>193</v>
-      </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G41" t="s">
         <v>22</v>
@@ -4016,19 +3447,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -4039,10 +3468,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4054,25 +3483,25 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
       </c>
       <c r="J2" t="s">
+        <v>196</v>
+      </c>
+      <c r="K2" t="s">
+        <v>197</v>
+      </c>
+      <c r="L2" t="s">
         <v>198</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>199</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>200</v>
-      </c>
-      <c r="M2" t="s">
-        <v>201</v>
-      </c>
-      <c r="N2" t="s">
-        <v>202</v>
       </c>
       <c r="O2" t="s">
         <v>14</v>
@@ -4086,16 +3515,16 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" t="s">
         <v>203</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>204</v>
-      </c>
-      <c r="D3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E3" t="s">
-        <v>206</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -4106,16 +3535,16 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" t="s">
         <v>207</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>208</v>
-      </c>
-      <c r="D4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" t="s">
-        <v>210</v>
       </c>
       <c r="F4" t="s">
         <v>27</v>
@@ -4126,16 +3555,16 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" t="s">
         <v>211</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>212</v>
-      </c>
-      <c r="D5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E5" t="s">
-        <v>214</v>
       </c>
       <c r="F5" t="s">
         <v>32</v>
@@ -4146,16 +3575,16 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" t="s">
         <v>215</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>216</v>
-      </c>
-      <c r="D6" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" t="s">
-        <v>218</v>
       </c>
       <c r="F6" t="s">
         <v>37</v>
@@ -4166,16 +3595,16 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" t="s">
         <v>219</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>220</v>
-      </c>
-      <c r="D7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E7" t="s">
-        <v>222</v>
       </c>
       <c r="F7" t="s">
         <v>42</v>
@@ -4186,16 +3615,16 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" t="s">
         <v>223</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>224</v>
-      </c>
-      <c r="D8" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" t="s">
-        <v>226</v>
       </c>
       <c r="F8" t="s">
         <v>47</v>
@@ -4206,16 +3635,16 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" t="s">
         <v>227</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>228</v>
-      </c>
-      <c r="D9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" t="s">
-        <v>230</v>
       </c>
       <c r="F9" t="s">
         <v>32</v>
@@ -4226,16 +3655,16 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" t="s">
         <v>231</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>232</v>
-      </c>
-      <c r="D10" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" t="s">
-        <v>234</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
@@ -4246,16 +3675,16 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" t="s">
         <v>235</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>236</v>
-      </c>
-      <c r="D11" t="s">
-        <v>237</v>
-      </c>
-      <c r="E11" t="s">
-        <v>238</v>
       </c>
       <c r="F11" t="s">
         <v>56</v>
@@ -4266,16 +3695,16 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" t="s">
         <v>239</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>240</v>
-      </c>
-      <c r="D12" t="s">
-        <v>241</v>
-      </c>
-      <c r="E12" t="s">
-        <v>242</v>
       </c>
       <c r="F12" t="s">
         <v>42</v>
@@ -4286,16 +3715,16 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" t="s">
         <v>243</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>244</v>
-      </c>
-      <c r="D13" t="s">
-        <v>245</v>
-      </c>
-      <c r="E13" t="s">
-        <v>246</v>
       </c>
       <c r="F13" t="s">
         <v>47</v>
@@ -4306,16 +3735,16 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" t="s">
+        <v>246</v>
+      </c>
+      <c r="D14" t="s">
         <v>247</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>248</v>
-      </c>
-      <c r="D14" t="s">
-        <v>249</v>
-      </c>
-      <c r="E14" t="s">
-        <v>250</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
@@ -4326,16 +3755,16 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" t="s">
         <v>251</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>252</v>
-      </c>
-      <c r="D15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E15" t="s">
-        <v>254</v>
       </c>
       <c r="F15" t="s">
         <v>32</v>
@@ -4346,16 +3775,16 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D16" t="s">
         <v>255</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>256</v>
-      </c>
-      <c r="D16" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" t="s">
-        <v>258</v>
       </c>
       <c r="F16" t="s">
         <v>47</v>
@@ -4366,16 +3795,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" t="s">
         <v>259</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>260</v>
-      </c>
-      <c r="D17" t="s">
-        <v>261</v>
-      </c>
-      <c r="E17" t="s">
-        <v>262</v>
       </c>
       <c r="F17" t="s">
         <v>56</v>
@@ -4386,19 +3815,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>261</v>
+      </c>
+      <c r="C18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" t="s">
         <v>263</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>264</v>
       </c>
-      <c r="D18" t="s">
-        <v>265</v>
-      </c>
-      <c r="E18" t="s">
-        <v>266</v>
-      </c>
       <c r="F18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
         <v>22</v>
@@ -4406,19 +3835,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
+        <v>265</v>
+      </c>
+      <c r="C19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" t="s">
         <v>267</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>268</v>
       </c>
-      <c r="D19" t="s">
-        <v>269</v>
-      </c>
-      <c r="E19" t="s">
-        <v>270</v>
-      </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
@@ -4426,19 +3855,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>272</v>
       </c>
-      <c r="D20" t="s">
-        <v>273</v>
-      </c>
-      <c r="E20" t="s">
-        <v>274</v>
-      </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G20" t="s">
         <v>22</v>
@@ -4446,19 +3875,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>273</v>
+      </c>
+      <c r="C21" t="s">
+        <v>274</v>
+      </c>
+      <c r="D21" t="s">
         <v>275</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>276</v>
       </c>
-      <c r="D21" t="s">
-        <v>277</v>
-      </c>
-      <c r="E21" t="s">
-        <v>278</v>
-      </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
         <v>22</v>
@@ -4466,19 +3895,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>277</v>
+      </c>
+      <c r="C22" t="s">
+        <v>278</v>
+      </c>
+      <c r="D22" t="s">
         <v>279</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>280</v>
       </c>
-      <c r="D22" t="s">
-        <v>281</v>
-      </c>
-      <c r="E22" t="s">
-        <v>282</v>
-      </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G22" t="s">
         <v>22</v>
@@ -4486,19 +3915,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>281</v>
+      </c>
+      <c r="C23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" t="s">
         <v>283</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>284</v>
       </c>
-      <c r="D23" t="s">
-        <v>285</v>
-      </c>
-      <c r="E23" t="s">
-        <v>286</v>
-      </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
         <v>22</v>
@@ -4506,19 +3935,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" t="s">
         <v>287</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>288</v>
       </c>
-      <c r="D24" t="s">
-        <v>289</v>
-      </c>
-      <c r="E24" t="s">
-        <v>290</v>
-      </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
         <v>22</v>
@@ -4526,16 +3955,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
+        <v>289</v>
+      </c>
+      <c r="C25" t="s">
+        <v>290</v>
+      </c>
+      <c r="D25" t="s">
         <v>291</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>292</v>
-      </c>
-      <c r="D25" t="s">
-        <v>293</v>
-      </c>
-      <c r="E25" t="s">
-        <v>294</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -4546,19 +3975,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>293</v>
+      </c>
+      <c r="C26" t="s">
+        <v>294</v>
+      </c>
+      <c r="D26" t="s">
         <v>295</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>296</v>
       </c>
-      <c r="D26" t="s">
-        <v>297</v>
-      </c>
-      <c r="E26" t="s">
-        <v>298</v>
-      </c>
       <c r="F26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
         <v>22</v>
@@ -4566,16 +3995,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C27" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" t="s">
         <v>299</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>300</v>
-      </c>
-      <c r="D27" t="s">
-        <v>301</v>
-      </c>
-      <c r="E27" t="s">
-        <v>302</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
@@ -4586,19 +4015,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>301</v>
+      </c>
+      <c r="C28" t="s">
+        <v>302</v>
+      </c>
+      <c r="D28" t="s">
         <v>303</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28" t="s">
         <v>304</v>
       </c>
-      <c r="D28" t="s">
-        <v>305</v>
-      </c>
-      <c r="E28" t="s">
-        <v>306</v>
-      </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G28" t="s">
         <v>22</v>
@@ -4606,19 +4035,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>305</v>
+      </c>
+      <c r="C29" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" t="s">
         <v>307</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
         <v>308</v>
       </c>
-      <c r="D29" t="s">
-        <v>309</v>
-      </c>
-      <c r="E29" t="s">
-        <v>310</v>
-      </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G29" t="s">
         <v>22</v>
@@ -4626,19 +4055,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>309</v>
+      </c>
+      <c r="C30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30" t="s">
         <v>311</v>
       </c>
-      <c r="C30" t="s">
+      <c r="E30" t="s">
         <v>312</v>
       </c>
-      <c r="D30" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" t="s">
-        <v>314</v>
-      </c>
       <c r="F30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G30" t="s">
         <v>22</v>
@@ -4646,16 +4075,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
+        <v>313</v>
+      </c>
+      <c r="C31" t="s">
+        <v>314</v>
+      </c>
+      <c r="D31" t="s">
         <v>315</v>
       </c>
-      <c r="C31" t="s">
+      <c r="E31" t="s">
         <v>316</v>
-      </c>
-      <c r="D31" t="s">
-        <v>317</v>
-      </c>
-      <c r="E31" t="s">
-        <v>318</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
@@ -4666,19 +4095,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>317</v>
+      </c>
+      <c r="C32" t="s">
+        <v>318</v>
+      </c>
+      <c r="D32" t="s">
         <v>319</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>320</v>
       </c>
-      <c r="D32" t="s">
-        <v>321</v>
-      </c>
-      <c r="E32" t="s">
-        <v>322</v>
-      </c>
       <c r="F32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s">
         <v>22</v>
@@ -4686,19 +4115,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
+        <v>321</v>
+      </c>
+      <c r="C33" t="s">
+        <v>322</v>
+      </c>
+      <c r="D33" t="s">
         <v>323</v>
       </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
         <v>324</v>
       </c>
-      <c r="D33" t="s">
-        <v>325</v>
-      </c>
-      <c r="E33" t="s">
-        <v>326</v>
-      </c>
       <c r="F33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G33" t="s">
         <v>22</v>
@@ -4706,16 +4135,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C34" t="s">
+        <v>326</v>
+      </c>
+      <c r="D34" t="s">
         <v>327</v>
       </c>
-      <c r="C34" t="s">
+      <c r="E34" t="s">
         <v>328</v>
-      </c>
-      <c r="D34" t="s">
-        <v>329</v>
-      </c>
-      <c r="E34" t="s">
-        <v>330</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -4726,16 +4155,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
+        <v>329</v>
+      </c>
+      <c r="C35" t="s">
+        <v>330</v>
+      </c>
+      <c r="D35" t="s">
         <v>331</v>
       </c>
-      <c r="C35" t="s">
+      <c r="E35" t="s">
         <v>332</v>
-      </c>
-      <c r="D35" t="s">
-        <v>333</v>
-      </c>
-      <c r="E35" t="s">
-        <v>334</v>
       </c>
       <c r="F35" t="s">
         <v>27</v>
@@ -4746,19 +4175,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
+        <v>333</v>
+      </c>
+      <c r="C36" t="s">
+        <v>334</v>
+      </c>
+      <c r="D36" t="s">
         <v>335</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E36" t="s">
         <v>336</v>
       </c>
-      <c r="D36" t="s">
-        <v>337</v>
-      </c>
-      <c r="E36" t="s">
-        <v>338</v>
-      </c>
       <c r="F36" t="s">
-        <v>339</v>
+        <v>721</v>
       </c>
       <c r="G36" t="s">
         <v>22</v>
@@ -4766,19 +4195,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" t="s">
+        <v>339</v>
+      </c>
+      <c r="E37" t="s">
         <v>340</v>
       </c>
-      <c r="C37" t="s">
-        <v>341</v>
-      </c>
-      <c r="D37" t="s">
-        <v>342</v>
-      </c>
-      <c r="E37" t="s">
-        <v>343</v>
-      </c>
       <c r="F37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
         <v>22</v>
@@ -4786,16 +4215,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
+        <v>341</v>
+      </c>
+      <c r="C38" t="s">
+        <v>342</v>
+      </c>
+      <c r="D38" t="s">
+        <v>343</v>
+      </c>
+      <c r="E38" t="s">
         <v>344</v>
-      </c>
-      <c r="C38" t="s">
-        <v>345</v>
-      </c>
-      <c r="D38" t="s">
-        <v>346</v>
-      </c>
-      <c r="E38" t="s">
-        <v>347</v>
       </c>
       <c r="F38" t="s">
         <v>47</v>
@@ -4806,19 +4235,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
+        <v>345</v>
+      </c>
+      <c r="C39" t="s">
+        <v>346</v>
+      </c>
+      <c r="D39" t="s">
+        <v>347</v>
+      </c>
+      <c r="E39" t="s">
         <v>348</v>
       </c>
-      <c r="C39" t="s">
-        <v>349</v>
-      </c>
-      <c r="D39" t="s">
-        <v>350</v>
-      </c>
-      <c r="E39" t="s">
-        <v>351</v>
-      </c>
       <c r="F39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G39" t="s">
         <v>22</v>
@@ -4826,16 +4255,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
+        <v>349</v>
+      </c>
+      <c r="C40" t="s">
+        <v>350</v>
+      </c>
+      <c r="D40" t="s">
+        <v>351</v>
+      </c>
+      <c r="E40" t="s">
         <v>352</v>
-      </c>
-      <c r="C40" t="s">
-        <v>353</v>
-      </c>
-      <c r="D40" t="s">
-        <v>354</v>
-      </c>
-      <c r="E40" t="s">
-        <v>355</v>
       </c>
       <c r="F40" t="s">
         <v>27</v>
@@ -4846,19 +4275,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
+        <v>353</v>
+      </c>
+      <c r="C41" t="s">
+        <v>354</v>
+      </c>
+      <c r="D41" t="s">
+        <v>355</v>
+      </c>
+      <c r="E41" t="s">
         <v>356</v>
       </c>
-      <c r="C41" t="s">
-        <v>357</v>
-      </c>
-      <c r="D41" t="s">
-        <v>358</v>
-      </c>
-      <c r="E41" t="s">
-        <v>359</v>
-      </c>
       <c r="F41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G41" t="s">
         <v>22</v>
@@ -4866,19 +4295,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AC41"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -4889,18 +4316,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D2" t="str">
-        <f>IF(TRIM(C2)="","",IF(LEN(C2)=2,LEFT(C2,1)&amp;"*",LEFT(C2,1)&amp;"*"&amp;RIGHT(C2,1)))</f>
-        <v>孙*</v>
+        <v>551</v>
+      </c>
+      <c r="D2" t="s">
+        <v>551</v>
       </c>
       <c r="E2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F2" t="str">
-        <f>IF(TRIM(E2)="","",IF(LEN(E2)=2,LEFT(E2,1)&amp;"*",LEFT(E2,1)&amp;"*"&amp;RIGHT(E2,1)))</f>
-        <v>李*</v>
+        <v>591</v>
+      </c>
+      <c r="F2" t="s">
+        <v>591</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
@@ -4915,10 +4340,10 @@
         <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="M2" t="s">
         <v>8</v>
@@ -4927,40 +4352,40 @@
         <v>9</v>
       </c>
       <c r="O2" t="s">
+        <v>359</v>
+      </c>
+      <c r="P2" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>361</v>
+      </c>
+      <c r="R2" t="s">
+        <v>362</v>
+      </c>
+      <c r="S2" t="s">
+        <v>363</v>
+      </c>
+      <c r="T2" t="s">
+        <v>200</v>
+      </c>
+      <c r="U2" t="s">
         <v>364</v>
       </c>
-      <c r="P2" t="s">
+      <c r="V2" t="s">
         <v>365</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="W2" t="s">
         <v>366</v>
       </c>
-      <c r="R2" t="s">
+      <c r="X2" t="s">
         <v>367</v>
       </c>
-      <c r="S2" t="s">
+      <c r="Y2" t="s">
         <v>368</v>
       </c>
-      <c r="T2" t="s">
-        <v>202</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="Z2" t="s">
         <v>369</v>
-      </c>
-      <c r="V2" t="s">
-        <v>370</v>
-      </c>
-      <c r="W2" t="s">
-        <v>371</v>
-      </c>
-      <c r="X2" t="s">
-        <v>372</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>373</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>374</v>
       </c>
       <c r="AA2" t="s">
         <v>14</v>
@@ -4974,138 +4399,128 @@
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E3" t="s">
+        <v>592</v>
+      </c>
+      <c r="F3" t="s">
+        <v>592</v>
+      </c>
+      <c r="G3" t="s">
+        <v>631</v>
+      </c>
+      <c r="H3" t="s">
+        <v>631</v>
+      </c>
+      <c r="I3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>670</v>
+      </c>
+      <c r="L3" t="s">
+        <v>670</v>
+      </c>
+      <c r="M3" t="s">
+        <v>371</v>
+      </c>
+      <c r="O3" t="s">
+        <v>372</v>
+      </c>
+      <c r="P3" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>374</v>
+      </c>
+      <c r="R3" t="s">
         <v>375</v>
       </c>
-      <c r="C3" t="s">
+      <c r="S3" t="s">
+        <v>722</v>
+      </c>
+      <c r="T3" t="s">
+        <v>709</v>
+      </c>
+      <c r="W3" t="s">
+        <v>371</v>
+      </c>
+      <c r="AB3" t="s">
         <v>376</v>
       </c>
-      <c r="D3" t="s">
+      <c r="AC3" t="s">
         <v>377</v>
-      </c>
-      <c r="E3" t="s">
-        <v>378</v>
-      </c>
-      <c r="F3" t="str">
-        <f t="shared" ref="F3:F41" si="0">IF(TRIM(E3)="","",IF(LEN(E3)=2,LEFT(E3,1)&amp;"*",LEFT(E3,1)&amp;"*"&amp;RIGHT(E3,1)))</f>
-        <v>白*梅</v>
-      </c>
-      <c r="G3" t="s">
-        <v>379</v>
-      </c>
-      <c r="H3" t="str">
-        <f>IF(LEN(G3)=1,G3,IF(LEN(G3)=2,LEFT(G3,1)&amp;"*",LEFT(G3,1)&amp;REPT("*",LEN(G3)-2)&amp;RIGHT(G3,2)))</f>
-        <v>新*********公司</v>
-      </c>
-      <c r="I3" t="s">
-        <v>380</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>378</v>
-      </c>
-      <c r="L3" t="str">
-        <f>IF(TRIM(K3)="","",IF(LEN(K3)=2,LEFT(K3,1)&amp;"*",LEFT(K3,1)&amp;"*"&amp;RIGHT(K3,1)))</f>
-        <v>白*梅</v>
-      </c>
-      <c r="M3" t="s">
-        <v>381</v>
-      </c>
-      <c r="O3" t="s">
-        <v>382</v>
-      </c>
-      <c r="P3" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>384</v>
-      </c>
-      <c r="R3" t="s">
-        <v>385</v>
-      </c>
-      <c r="S3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T3" t="s">
-        <v>386</v>
-      </c>
-      <c r="W3" t="s">
-        <v>381</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>387</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" t="s">
-        <v>389</v>
+        <v>513</v>
       </c>
       <c r="C4" t="s">
-        <v>390</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" ref="D4:D40" si="1">IF(TRIM(C4)="","",IF(LEN(C4)=2,LEFT(C4,1)&amp;"*",LEFT(C4,1)&amp;"*"&amp;RIGHT(C4,1)))</f>
-        <v>张*英</v>
+        <v>553</v>
+      </c>
+      <c r="D4" t="s">
+        <v>553</v>
       </c>
       <c r="E4" t="s">
-        <v>391</v>
-      </c>
-      <c r="F4" t="str">
-        <f t="shared" si="0"/>
-        <v>包*忠</v>
+        <v>593</v>
+      </c>
+      <c r="F4" t="s">
+        <v>593</v>
       </c>
       <c r="G4" t="s">
-        <v>392</v>
-      </c>
-      <c r="H4" t="str">
-        <f t="shared" ref="H4:H41" si="2">IF(LEN(G4)=1,G4,IF(LEN(G4)=2,LEFT(G4,1)&amp;"*",LEFT(G4,1)&amp;REPT("*",LEN(G4)-2)&amp;RIGHT(G4,2)))</f>
-        <v>维******公司</v>
+        <v>632</v>
+      </c>
+      <c r="H4" t="s">
+        <v>632</v>
       </c>
       <c r="I4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J4" t="s">
         <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>391</v>
-      </c>
-      <c r="L4" t="str">
-        <f t="shared" ref="L4:L41" si="3">IF(TRIM(K4)="","",IF(LEN(K4)=2,LEFT(K4,1)&amp;"*",LEFT(K4,1)&amp;"*"&amp;RIGHT(K4,1)))</f>
-        <v>包*忠</v>
+        <v>671</v>
+      </c>
+      <c r="L4" t="s">
+        <v>671</v>
       </c>
       <c r="Q4" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:29">
       <c r="A5" t="s">
-        <v>394</v>
+        <v>514</v>
       </c>
       <c r="C5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="1"/>
-        <v>邓*</v>
+        <v>554</v>
+      </c>
+      <c r="D5" t="s">
+        <v>554</v>
       </c>
       <c r="E5" t="s">
-        <v>396</v>
-      </c>
-      <c r="F5" t="str">
-        <f t="shared" si="0"/>
-        <v>包*路</v>
+        <v>594</v>
+      </c>
+      <c r="F5" t="s">
+        <v>594</v>
       </c>
       <c r="G5" t="s">
-        <v>397</v>
-      </c>
-      <c r="H5" t="str">
-        <f t="shared" si="2"/>
-        <v>陈*</v>
+        <v>633</v>
+      </c>
+      <c r="H5" t="s">
+        <v>633</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -5114,40 +4529,36 @@
         <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>396</v>
-      </c>
-      <c r="L5" t="str">
-        <f t="shared" si="3"/>
-        <v>包*路</v>
+        <v>672</v>
+      </c>
+      <c r="L5" t="s">
+        <v>672</v>
       </c>
       <c r="Q5" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:29">
       <c r="A6" t="s">
-        <v>398</v>
+        <v>515</v>
       </c>
       <c r="C6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D6" t="str">
-        <f t="shared" si="1"/>
-        <v>张*</v>
+        <v>555</v>
+      </c>
+      <c r="D6" t="s">
+        <v>555</v>
       </c>
       <c r="E6" t="s">
-        <v>400</v>
-      </c>
-      <c r="F6" t="str">
-        <f t="shared" si="0"/>
-        <v>江*</v>
+        <v>595</v>
+      </c>
+      <c r="F6" t="s">
+        <v>595</v>
       </c>
       <c r="G6" t="s">
-        <v>401</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="2"/>
-        <v>联******公司</v>
+        <v>634</v>
+      </c>
+      <c r="H6" t="s">
+        <v>634</v>
       </c>
       <c r="I6" t="s">
         <v>42</v>
@@ -5156,102 +4567,95 @@
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>402</v>
-      </c>
-      <c r="L6" t="str">
-        <f t="shared" si="3"/>
-        <v>张*</v>
+        <v>673</v>
+      </c>
+      <c r="L6" t="s">
+        <v>673</v>
       </c>
       <c r="Q6" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:29">
       <c r="A7" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="C7" t="s">
-        <v>404</v>
+        <v>556</v>
       </c>
       <c r="D7" t="s">
-        <v>405</v>
+        <v>556</v>
       </c>
       <c r="E7" t="s">
-        <v>406</v>
-      </c>
-      <c r="F7" t="str">
-        <f t="shared" si="0"/>
-        <v>刘*</v>
+        <v>596</v>
+      </c>
+      <c r="F7" t="s">
+        <v>596</v>
       </c>
       <c r="G7" t="s">
-        <v>407</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="2"/>
-        <v>许*</v>
+        <v>635</v>
+      </c>
+      <c r="H7" t="s">
+        <v>635</v>
       </c>
       <c r="I7" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="J7" t="s">
         <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>409</v>
-      </c>
-      <c r="L7" t="str">
-        <f t="shared" si="3"/>
-        <v>曹*英</v>
+        <v>674</v>
+      </c>
+      <c r="L7" t="s">
+        <v>674</v>
       </c>
       <c r="M7" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="O7" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P7" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q7" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R7" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S7" t="s">
-        <v>411</v>
+        <v>723</v>
       </c>
       <c r="AB7" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="AC7" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" t="s">
-        <v>413</v>
+        <v>517</v>
       </c>
       <c r="C8" t="s">
-        <v>414</v>
-      </c>
-      <c r="D8" t="str">
-        <f t="shared" si="1"/>
-        <v>沙*</v>
+        <v>557</v>
+      </c>
+      <c r="D8" t="s">
+        <v>557</v>
       </c>
       <c r="E8" t="s">
-        <v>415</v>
-      </c>
-      <c r="F8" t="str">
-        <f t="shared" si="0"/>
-        <v>晁*童</v>
+        <v>597</v>
+      </c>
+      <c r="F8" t="s">
+        <v>597</v>
       </c>
       <c r="G8" t="s">
-        <v>416</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="2"/>
-        <v>鑫********公司</v>
+        <v>636</v>
+      </c>
+      <c r="H8" t="s">
+        <v>636</v>
       </c>
       <c r="I8" t="s">
         <v>47</v>
@@ -5260,121 +4664,112 @@
         <v>22</v>
       </c>
       <c r="K8" t="s">
-        <v>415</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="3"/>
-        <v>晁*童</v>
+        <v>675</v>
+      </c>
+      <c r="L8" t="s">
+        <v>675</v>
       </c>
       <c r="Q8" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:29">
       <c r="A9" t="s">
-        <v>417</v>
+        <v>518</v>
       </c>
       <c r="C9" t="s">
-        <v>418</v>
+        <v>558</v>
       </c>
       <c r="D9" t="s">
-        <v>418</v>
+        <v>558</v>
       </c>
       <c r="E9" t="s">
-        <v>419</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" si="0"/>
-        <v>何*</v>
+        <v>598</v>
+      </c>
+      <c r="F9" t="s">
+        <v>598</v>
       </c>
       <c r="G9" t="s">
-        <v>420</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="2"/>
-        <v>网********公司</v>
+        <v>637</v>
+      </c>
+      <c r="H9" t="s">
+        <v>637</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9" t="s">
         <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>421</v>
-      </c>
-      <c r="L9" t="str">
-        <f t="shared" si="3"/>
-        <v>刘*</v>
+        <v>676</v>
+      </c>
+      <c r="L9" t="s">
+        <v>676</v>
       </c>
       <c r="Q9" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:29">
       <c r="A10" t="s">
-        <v>422</v>
+        <v>519</v>
       </c>
       <c r="C10" t="s">
-        <v>423</v>
+        <v>559</v>
       </c>
       <c r="D10" t="s">
-        <v>423</v>
+        <v>559</v>
       </c>
       <c r="E10" t="s">
-        <v>362</v>
-      </c>
-      <c r="F10" t="str">
-        <f t="shared" si="0"/>
-        <v>李*</v>
+        <v>599</v>
+      </c>
+      <c r="F10" t="s">
+        <v>599</v>
       </c>
       <c r="G10" t="s">
-        <v>424</v>
-      </c>
-      <c r="H10" t="str">
-        <f t="shared" si="2"/>
-        <v>泰*******公司</v>
+        <v>638</v>
+      </c>
+      <c r="H10" t="s">
+        <v>638</v>
       </c>
       <c r="I10" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="J10" t="s">
         <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>425</v>
-      </c>
-      <c r="L10" t="str">
-        <f t="shared" si="3"/>
-        <v>陶*梅</v>
+        <v>677</v>
+      </c>
+      <c r="L10" t="s">
+        <v>677</v>
       </c>
       <c r="Q10" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:29">
       <c r="A11" t="s">
-        <v>426</v>
+        <v>520</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="D11" t="s">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="E11" t="s">
-        <v>428</v>
-      </c>
-      <c r="F11" t="str">
-        <f t="shared" si="0"/>
-        <v>王*</v>
+        <v>600</v>
+      </c>
+      <c r="F11" t="s">
+        <v>600</v>
       </c>
       <c r="G11" t="s">
-        <v>429</v>
-      </c>
-      <c r="H11" t="str">
-        <f t="shared" si="2"/>
-        <v>维*******公司</v>
+        <v>639</v>
+      </c>
+      <c r="H11" t="s">
+        <v>639</v>
       </c>
       <c r="I11" t="s">
         <v>21</v>
@@ -5383,108 +4778,101 @@
         <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>430</v>
-      </c>
-      <c r="L11" t="str">
-        <f t="shared" si="3"/>
-        <v>孙*</v>
+        <v>678</v>
+      </c>
+      <c r="L11" t="s">
+        <v>678</v>
       </c>
       <c r="Q11" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:29">
       <c r="A12" t="s">
-        <v>431</v>
+        <v>521</v>
       </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>561</v>
       </c>
       <c r="D12" t="s">
-        <v>432</v>
+        <v>561</v>
       </c>
       <c r="E12" t="s">
-        <v>433</v>
-      </c>
-      <c r="F12" t="str">
-        <f t="shared" si="0"/>
-        <v>陈*</v>
+        <v>601</v>
+      </c>
+      <c r="F12" t="s">
+        <v>601</v>
       </c>
       <c r="G12" t="s">
-        <v>434</v>
-      </c>
-      <c r="H12" t="str">
-        <f t="shared" si="2"/>
-        <v>惠**********公司</v>
+        <v>640</v>
+      </c>
+      <c r="H12" t="s">
+        <v>640</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
       </c>
       <c r="K12" t="s">
-        <v>435</v>
-      </c>
-      <c r="L12" t="str">
-        <f t="shared" si="3"/>
-        <v>张*</v>
+        <v>679</v>
+      </c>
+      <c r="L12" t="s">
+        <v>679</v>
       </c>
       <c r="M12" t="s">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="O12" t="s">
+        <v>372</v>
+      </c>
+      <c r="P12" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>374</v>
+      </c>
+      <c r="R12" t="s">
+        <v>375</v>
+      </c>
+      <c r="S12" t="s">
+        <v>722</v>
+      </c>
+      <c r="T12" t="s">
+        <v>710</v>
+      </c>
+      <c r="W12" t="s">
         <v>382</v>
       </c>
-      <c r="P12" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>384</v>
-      </c>
-      <c r="R12" t="s">
-        <v>385</v>
-      </c>
-      <c r="S12" t="s">
-        <v>59</v>
-      </c>
-      <c r="T12" t="s">
-        <v>437</v>
-      </c>
-      <c r="W12" t="s">
-        <v>436</v>
-      </c>
       <c r="AB12" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC12" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:29">
       <c r="A13" t="s">
-        <v>438</v>
+        <v>522</v>
       </c>
       <c r="C13" t="s">
-        <v>439</v>
-      </c>
-      <c r="D13" t="str">
-        <f t="shared" si="1"/>
-        <v>柴*</v>
+        <v>562</v>
+      </c>
+      <c r="D13" t="s">
+        <v>562</v>
       </c>
       <c r="E13" t="s">
-        <v>440</v>
-      </c>
-      <c r="F13" t="str">
-        <f t="shared" si="0"/>
-        <v>侯*兰</v>
+        <v>602</v>
+      </c>
+      <c r="F13" t="s">
+        <v>602</v>
       </c>
       <c r="G13" t="s">
-        <v>441</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" si="2"/>
-        <v>巨******公司</v>
+        <v>641</v>
+      </c>
+      <c r="H13" t="s">
+        <v>641</v>
       </c>
       <c r="I13" t="s">
         <v>27</v>
@@ -5493,39 +4881,36 @@
         <v>22</v>
       </c>
       <c r="K13" t="s">
-        <v>442</v>
-      </c>
-      <c r="L13" t="str">
-        <f t="shared" si="3"/>
-        <v>王*</v>
+        <v>680</v>
+      </c>
+      <c r="L13" t="s">
+        <v>680</v>
       </c>
       <c r="Q13" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:29">
       <c r="A14" t="s">
-        <v>443</v>
+        <v>523</v>
       </c>
       <c r="C14" t="s">
-        <v>444</v>
+        <v>563</v>
       </c>
       <c r="D14" t="s">
-        <v>445</v>
+        <v>563</v>
       </c>
       <c r="E14" t="s">
-        <v>446</v>
-      </c>
-      <c r="F14" t="str">
-        <f t="shared" si="0"/>
-        <v>李*</v>
+        <v>603</v>
+      </c>
+      <c r="F14" t="s">
+        <v>603</v>
       </c>
       <c r="G14" t="s">
-        <v>447</v>
-      </c>
-      <c r="H14" t="str">
-        <f t="shared" si="2"/>
-        <v>天******公司</v>
+        <v>642</v>
+      </c>
+      <c r="H14" t="s">
+        <v>642</v>
       </c>
       <c r="I14" t="s">
         <v>42</v>
@@ -5534,81 +4919,74 @@
         <v>22</v>
       </c>
       <c r="K14" t="s">
-        <v>448</v>
-      </c>
-      <c r="L14" t="str">
-        <f t="shared" si="3"/>
-        <v>谢*梅</v>
+        <v>681</v>
+      </c>
+      <c r="L14" t="s">
+        <v>681</v>
       </c>
       <c r="Q14" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:29">
       <c r="A15" t="s">
-        <v>449</v>
+        <v>524</v>
       </c>
       <c r="C15" t="s">
-        <v>450</v>
-      </c>
-      <c r="D15" t="str">
-        <f t="shared" si="1"/>
-        <v>李*</v>
+        <v>564</v>
+      </c>
+      <c r="D15" t="s">
+        <v>564</v>
       </c>
       <c r="E15" t="s">
-        <v>451</v>
-      </c>
-      <c r="F15" t="str">
-        <f t="shared" si="0"/>
-        <v>王*</v>
+        <v>604</v>
+      </c>
+      <c r="F15" t="s">
+        <v>604</v>
       </c>
       <c r="G15" t="s">
-        <v>452</v>
-      </c>
-      <c r="H15" t="str">
-        <f t="shared" si="2"/>
-        <v>开*********公司</v>
+        <v>643</v>
+      </c>
+      <c r="H15" t="s">
+        <v>643</v>
       </c>
       <c r="I15" t="s">
-        <v>453</v>
+        <v>383</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
       </c>
       <c r="K15" t="s">
-        <v>454</v>
-      </c>
-      <c r="L15" t="str">
-        <f t="shared" si="3"/>
-        <v>赵*珍</v>
+        <v>682</v>
+      </c>
+      <c r="L15" t="s">
+        <v>682</v>
       </c>
       <c r="Q15" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:29">
       <c r="A16" t="s">
-        <v>455</v>
+        <v>525</v>
       </c>
       <c r="C16" t="s">
-        <v>456</v>
+        <v>565</v>
       </c>
       <c r="D16" t="s">
-        <v>456</v>
+        <v>565</v>
       </c>
       <c r="E16" t="s">
-        <v>457</v>
-      </c>
-      <c r="F16" t="str">
-        <f t="shared" si="0"/>
-        <v>徐*丽</v>
+        <v>605</v>
+      </c>
+      <c r="F16" t="s">
+        <v>605</v>
       </c>
       <c r="G16" t="s">
-        <v>458</v>
-      </c>
-      <c r="H16" t="str">
-        <f t="shared" si="2"/>
-        <v>群******公司</v>
+        <v>644</v>
+      </c>
+      <c r="H16" t="s">
+        <v>644</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -5617,51 +4995,48 @@
         <v>22</v>
       </c>
       <c r="K16" t="s">
-        <v>459</v>
-      </c>
-      <c r="L16" t="str">
-        <f t="shared" si="3"/>
-        <v>王*军</v>
+        <v>683</v>
+      </c>
+      <c r="L16" t="s">
+        <v>683</v>
       </c>
       <c r="M16" t="s">
-        <v>460</v>
+        <v>384</v>
       </c>
       <c r="O16" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P16" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q16" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="S16" t="s">
-        <v>461</v>
+        <v>724</v>
       </c>
     </row>
     <row r="17" spans="1:29">
       <c r="A17" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="C17" t="s">
-        <v>456</v>
+        <v>566</v>
       </c>
       <c r="D17" t="s">
-        <v>456</v>
+        <v>566</v>
       </c>
       <c r="E17" t="s">
-        <v>463</v>
-      </c>
-      <c r="F17" t="str">
-        <f t="shared" si="0"/>
-        <v>郑*华</v>
+        <v>606</v>
+      </c>
+      <c r="F17" t="s">
+        <v>606</v>
       </c>
       <c r="G17" t="s">
-        <v>464</v>
-      </c>
-      <c r="H17" t="str">
-        <f t="shared" si="2"/>
-        <v>昂********公司</v>
+        <v>645</v>
+      </c>
+      <c r="H17" t="s">
+        <v>645</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -5670,51 +5045,48 @@
         <v>22</v>
       </c>
       <c r="K17" t="s">
-        <v>465</v>
-      </c>
-      <c r="L17" t="str">
-        <f t="shared" si="3"/>
-        <v>赵*</v>
+        <v>684</v>
+      </c>
+      <c r="L17" t="s">
+        <v>684</v>
       </c>
       <c r="M17" t="s">
-        <v>466</v>
+        <v>385</v>
       </c>
       <c r="O17" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P17" t="s">
-        <v>467</v>
+        <v>386</v>
       </c>
       <c r="Q17" t="s">
-        <v>468</v>
+        <v>387</v>
       </c>
       <c r="S17" t="s">
-        <v>469</v>
+        <v>725</v>
       </c>
     </row>
     <row r="18" spans="1:29">
       <c r="A18" t="s">
-        <v>470</v>
+        <v>527</v>
       </c>
       <c r="C18" t="s">
-        <v>471</v>
+        <v>567</v>
       </c>
       <c r="D18" t="s">
-        <v>471</v>
+        <v>567</v>
       </c>
       <c r="E18" t="s">
-        <v>472</v>
-      </c>
-      <c r="F18" t="str">
-        <f t="shared" si="0"/>
-        <v>程*</v>
+        <v>607</v>
+      </c>
+      <c r="F18" t="s">
+        <v>607</v>
       </c>
       <c r="G18" t="s">
-        <v>473</v>
-      </c>
-      <c r="H18" t="str">
-        <f t="shared" si="2"/>
-        <v>诺*********公司</v>
+        <v>646</v>
+      </c>
+      <c r="H18" t="s">
+        <v>646</v>
       </c>
       <c r="I18" t="s">
         <v>47</v>
@@ -5723,207 +5095,188 @@
         <v>22</v>
       </c>
       <c r="K18" t="s">
-        <v>472</v>
-      </c>
-      <c r="L18" t="str">
-        <f t="shared" si="3"/>
-        <v>程*</v>
+        <v>685</v>
+      </c>
+      <c r="L18" t="s">
+        <v>685</v>
       </c>
       <c r="Q18" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:29">
       <c r="A19" t="s">
-        <v>474</v>
+        <v>528</v>
       </c>
       <c r="C19" t="s">
-        <v>475</v>
+        <v>568</v>
       </c>
       <c r="D19" t="s">
-        <v>475</v>
+        <v>568</v>
       </c>
       <c r="E19" t="s">
-        <v>476</v>
-      </c>
-      <c r="F19" t="str">
-        <f t="shared" si="0"/>
-        <v>宾*</v>
+        <v>608</v>
+      </c>
+      <c r="F19" t="s">
+        <v>608</v>
       </c>
       <c r="G19" t="s">
-        <v>477</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="2"/>
-        <v>图********公司</v>
+        <v>647</v>
+      </c>
+      <c r="H19" t="s">
+        <v>647</v>
       </c>
       <c r="I19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
       </c>
       <c r="K19" t="s">
-        <v>478</v>
-      </c>
-      <c r="L19" t="str">
-        <f t="shared" si="3"/>
-        <v>姜*</v>
+        <v>686</v>
+      </c>
+      <c r="L19" t="s">
+        <v>686</v>
       </c>
       <c r="Q19" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:29">
       <c r="A20" t="s">
-        <v>479</v>
+        <v>529</v>
       </c>
       <c r="C20" t="s">
-        <v>480</v>
-      </c>
-      <c r="D20" t="str">
-        <f t="shared" si="1"/>
-        <v>李*霞</v>
+        <v>569</v>
+      </c>
+      <c r="D20" t="s">
+        <v>569</v>
       </c>
       <c r="E20" t="s">
-        <v>481</v>
-      </c>
-      <c r="F20" t="str">
-        <f t="shared" si="0"/>
-        <v>单*芳</v>
+        <v>609</v>
+      </c>
+      <c r="F20" t="s">
+        <v>609</v>
       </c>
       <c r="G20" t="s">
-        <v>482</v>
-      </c>
-      <c r="H20" t="str">
-        <f t="shared" si="2"/>
-        <v>天******公司</v>
+        <v>648</v>
+      </c>
+      <c r="H20" t="s">
+        <v>648</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
       </c>
       <c r="K20" t="s">
-        <v>481</v>
-      </c>
-      <c r="L20" t="str">
-        <f t="shared" si="3"/>
-        <v>单*芳</v>
+        <v>687</v>
+      </c>
+      <c r="L20" t="s">
+        <v>687</v>
       </c>
       <c r="Q20" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:29">
       <c r="A21" t="s">
-        <v>483</v>
+        <v>530</v>
       </c>
       <c r="C21" t="s">
-        <v>484</v>
-      </c>
-      <c r="D21" t="str">
-        <f t="shared" si="1"/>
-        <v>李*</v>
+        <v>570</v>
+      </c>
+      <c r="D21" t="s">
+        <v>570</v>
       </c>
       <c r="E21" t="s">
-        <v>485</v>
-      </c>
-      <c r="F21" t="str">
-        <f t="shared" si="0"/>
-        <v>陈*</v>
+        <v>610</v>
+      </c>
+      <c r="F21" t="s">
+        <v>610</v>
       </c>
       <c r="G21" t="s">
-        <v>486</v>
-      </c>
-      <c r="H21" t="str">
-        <f t="shared" si="2"/>
-        <v>诺*********公司</v>
+        <v>649</v>
+      </c>
+      <c r="H21" t="s">
+        <v>649</v>
       </c>
       <c r="I21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
       </c>
       <c r="K21" t="s">
-        <v>487</v>
-      </c>
-      <c r="L21" t="str">
-        <f t="shared" si="3"/>
-        <v>程*</v>
+        <v>688</v>
+      </c>
+      <c r="L21" t="s">
+        <v>688</v>
       </c>
       <c r="Q21" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:29">
       <c r="A22" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="C22" t="s">
-        <v>489</v>
-      </c>
-      <c r="D22" t="str">
-        <f t="shared" si="1"/>
-        <v>马*</v>
+        <v>571</v>
+      </c>
+      <c r="D22" t="s">
+        <v>571</v>
       </c>
       <c r="E22" t="s">
-        <v>490</v>
-      </c>
-      <c r="F22" t="str">
-        <f t="shared" si="0"/>
-        <v>高*</v>
+        <v>611</v>
+      </c>
+      <c r="F22" t="s">
+        <v>611</v>
       </c>
       <c r="G22" t="s">
-        <v>491</v>
-      </c>
-      <c r="H22" t="str">
-        <f t="shared" si="2"/>
-        <v>信********公司</v>
+        <v>650</v>
+      </c>
+      <c r="H22" t="s">
+        <v>650</v>
       </c>
       <c r="I22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
       </c>
       <c r="K22" t="s">
-        <v>492</v>
-      </c>
-      <c r="L22" t="str">
-        <f t="shared" si="3"/>
-        <v>程*</v>
+        <v>689</v>
+      </c>
+      <c r="L22" t="s">
+        <v>689</v>
       </c>
       <c r="Q22" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:29">
       <c r="A23" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="C23" t="s">
-        <v>494</v>
-      </c>
-      <c r="D23" t="str">
-        <f t="shared" si="1"/>
-        <v>吴*</v>
+        <v>572</v>
+      </c>
+      <c r="D23" t="s">
+        <v>572</v>
       </c>
       <c r="E23" t="s">
-        <v>495</v>
-      </c>
-      <c r="F23" t="str">
-        <f t="shared" si="0"/>
-        <v>董*</v>
+        <v>612</v>
+      </c>
+      <c r="F23" t="s">
+        <v>612</v>
       </c>
       <c r="G23" t="s">
-        <v>496</v>
-      </c>
-      <c r="H23" t="str">
-        <f t="shared" si="2"/>
-        <v>海******公司</v>
+        <v>651</v>
+      </c>
+      <c r="H23" t="s">
+        <v>651</v>
       </c>
       <c r="I23" t="s">
         <v>32</v>
@@ -5932,103 +5285,95 @@
         <v>22</v>
       </c>
       <c r="K23" t="s">
-        <v>495</v>
-      </c>
-      <c r="L23" t="str">
-        <f t="shared" si="3"/>
-        <v>董*</v>
+        <v>690</v>
+      </c>
+      <c r="L23" t="s">
+        <v>690</v>
       </c>
       <c r="Q23" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:29">
       <c r="A24" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="C24" t="s">
-        <v>498</v>
-      </c>
-      <c r="D24" t="str">
-        <f t="shared" si="1"/>
-        <v>高*</v>
+        <v>573</v>
+      </c>
+      <c r="D24" t="s">
+        <v>573</v>
       </c>
       <c r="E24" t="s">
-        <v>499</v>
-      </c>
-      <c r="F24" t="str">
-        <f t="shared" si="0"/>
-        <v>窦*</v>
+        <v>613</v>
+      </c>
+      <c r="F24" t="s">
+        <v>613</v>
       </c>
       <c r="G24" t="s">
-        <v>500</v>
-      </c>
-      <c r="H24" t="str">
-        <f t="shared" si="2"/>
-        <v>济*********公司</v>
+        <v>652</v>
+      </c>
+      <c r="H24" t="s">
+        <v>652</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
       </c>
       <c r="K24" t="s">
-        <v>499</v>
-      </c>
-      <c r="L24" t="str">
-        <f t="shared" si="3"/>
-        <v>窦*</v>
+        <v>691</v>
+      </c>
+      <c r="L24" t="s">
+        <v>691</v>
       </c>
       <c r="M24" t="s">
-        <v>501</v>
+        <v>388</v>
       </c>
       <c r="O24" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P24" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q24" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R24" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S24" t="s">
-        <v>502</v>
+        <v>722</v>
       </c>
       <c r="T24" t="s">
-        <v>503</v>
+        <v>711</v>
       </c>
       <c r="W24" t="s">
-        <v>501</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" spans="1:29">
       <c r="A25" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="C25" t="s">
-        <v>505</v>
-      </c>
-      <c r="D25" t="str">
-        <f t="shared" si="1"/>
-        <v>刘*梅</v>
+        <v>574</v>
+      </c>
+      <c r="D25" t="s">
+        <v>574</v>
       </c>
       <c r="E25" t="s">
-        <v>506</v>
-      </c>
-      <c r="F25" t="str">
-        <f t="shared" si="0"/>
-        <v>程*英</v>
+        <v>614</v>
+      </c>
+      <c r="F25" t="s">
+        <v>614</v>
       </c>
       <c r="G25" t="s">
-        <v>507</v>
-      </c>
-      <c r="H25" t="str">
-        <f t="shared" si="2"/>
-        <v>襄*********公司</v>
+        <v>653</v>
+      </c>
+      <c r="H25" t="s">
+        <v>653</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -6037,67 +5382,63 @@
         <v>22</v>
       </c>
       <c r="K25" t="s">
-        <v>508</v>
-      </c>
-      <c r="L25" t="str">
-        <f t="shared" si="3"/>
-        <v>叶*</v>
+        <v>692</v>
+      </c>
+      <c r="L25" t="s">
+        <v>692</v>
       </c>
       <c r="M25" t="s">
-        <v>509</v>
+        <v>389</v>
       </c>
       <c r="O25" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P25" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q25" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R25" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S25" t="s">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="T25" t="s">
-        <v>511</v>
+        <v>712</v>
       </c>
       <c r="W25" t="s">
-        <v>509</v>
+        <v>389</v>
       </c>
       <c r="AB25" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC25" t="s">
-        <v>512</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26" spans="1:29">
       <c r="A26" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="C26" t="s">
-        <v>514</v>
-      </c>
-      <c r="D26" t="str">
-        <f t="shared" si="1"/>
-        <v>丁*</v>
+        <v>575</v>
+      </c>
+      <c r="D26" t="s">
+        <v>575</v>
       </c>
       <c r="E26" t="s">
-        <v>515</v>
-      </c>
-      <c r="F26" t="str">
-        <f t="shared" si="0"/>
-        <v>程*</v>
+        <v>615</v>
+      </c>
+      <c r="F26" t="s">
+        <v>615</v>
       </c>
       <c r="G26" t="s">
-        <v>516</v>
-      </c>
-      <c r="H26" t="str">
-        <f t="shared" si="2"/>
-        <v>网********公司</v>
+        <v>654</v>
+      </c>
+      <c r="H26" t="s">
+        <v>654</v>
       </c>
       <c r="I26" t="s">
         <v>21</v>
@@ -6106,235 +5447,219 @@
         <v>22</v>
       </c>
       <c r="K26" t="s">
-        <v>517</v>
-      </c>
-      <c r="L26" t="str">
-        <f t="shared" si="3"/>
-        <v>徐*英</v>
+        <v>693</v>
+      </c>
+      <c r="L26" t="s">
+        <v>693</v>
       </c>
       <c r="M26" t="s">
-        <v>518</v>
+        <v>391</v>
       </c>
       <c r="O26" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P26" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q26" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R26" t="s">
-        <v>519</v>
+        <v>392</v>
       </c>
       <c r="S26" t="s">
-        <v>469</v>
+        <v>724</v>
       </c>
       <c r="AB26" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC26" t="s">
-        <v>512</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:29">
       <c r="A27" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="C27" t="s">
-        <v>521</v>
-      </c>
-      <c r="D27" t="str">
-        <f t="shared" si="1"/>
-        <v>陈*华</v>
+        <v>576</v>
+      </c>
+      <c r="D27" t="s">
+        <v>576</v>
       </c>
       <c r="E27" t="s">
-        <v>522</v>
-      </c>
-      <c r="F27" t="str">
-        <f t="shared" si="0"/>
-        <v>杜*</v>
+        <v>616</v>
+      </c>
+      <c r="F27" t="s">
+        <v>616</v>
       </c>
       <c r="G27" t="s">
-        <v>523</v>
-      </c>
-      <c r="H27" t="str">
-        <f t="shared" si="2"/>
-        <v>商********公司</v>
+        <v>655</v>
+      </c>
+      <c r="H27" t="s">
+        <v>655</v>
       </c>
       <c r="I27" t="s">
-        <v>524</v>
+        <v>718</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
       </c>
       <c r="K27" t="s">
-        <v>522</v>
-      </c>
-      <c r="L27" t="str">
-        <f t="shared" si="3"/>
-        <v>杜*</v>
+        <v>694</v>
+      </c>
+      <c r="L27" t="s">
+        <v>694</v>
       </c>
       <c r="M27" t="s">
-        <v>525</v>
+        <v>393</v>
       </c>
       <c r="O27" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P27" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q27" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R27" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S27" t="s">
-        <v>526</v>
+        <v>725</v>
       </c>
       <c r="T27" t="s">
-        <v>527</v>
+        <v>713</v>
       </c>
       <c r="W27" t="s">
-        <v>525</v>
+        <v>393</v>
       </c>
       <c r="AB27" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC27" t="s">
-        <v>512</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:29">
       <c r="A28" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C28" t="s">
-        <v>529</v>
-      </c>
-      <c r="D28" t="str">
-        <f t="shared" si="1"/>
-        <v>张*</v>
+        <v>577</v>
+      </c>
+      <c r="D28" t="s">
+        <v>577</v>
       </c>
       <c r="E28" t="s">
-        <v>522</v>
-      </c>
-      <c r="F28" t="str">
-        <f t="shared" si="0"/>
-        <v>杜*</v>
+        <v>617</v>
+      </c>
+      <c r="F28" t="s">
+        <v>617</v>
       </c>
       <c r="G28" t="s">
-        <v>530</v>
-      </c>
-      <c r="H28" t="str">
-        <f t="shared" si="2"/>
-        <v>合********公司</v>
+        <v>656</v>
+      </c>
+      <c r="H28" t="s">
+        <v>656</v>
       </c>
       <c r="I28" t="s">
-        <v>507</v>
+        <v>719</v>
       </c>
       <c r="J28" t="s">
         <v>22</v>
       </c>
       <c r="K28" t="s">
-        <v>522</v>
-      </c>
-      <c r="L28" t="str">
-        <f t="shared" si="3"/>
-        <v>杜*</v>
+        <v>695</v>
+      </c>
+      <c r="L28" t="s">
+        <v>695</v>
       </c>
       <c r="M28" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="O28" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P28" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q28" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R28" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S28" t="s">
-        <v>411</v>
+        <v>723</v>
       </c>
       <c r="AB28" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="AC28" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:29">
       <c r="A29" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C29" t="s">
-        <v>532</v>
-      </c>
-      <c r="D29" t="str">
-        <f t="shared" si="1"/>
-        <v>赵*</v>
+        <v>578</v>
+      </c>
+      <c r="D29" t="s">
+        <v>578</v>
       </c>
       <c r="E29" t="s">
-        <v>533</v>
-      </c>
-      <c r="F29" t="str">
-        <f t="shared" si="0"/>
-        <v>段*</v>
+        <v>618</v>
+      </c>
+      <c r="F29" t="s">
+        <v>618</v>
       </c>
       <c r="G29" t="s">
-        <v>534</v>
-      </c>
-      <c r="H29" t="str">
-        <f t="shared" si="2"/>
-        <v>国******公司</v>
+        <v>657</v>
+      </c>
+      <c r="H29" t="s">
+        <v>657</v>
       </c>
       <c r="I29" t="s">
-        <v>453</v>
+        <v>383</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>533</v>
-      </c>
-      <c r="L29" t="str">
-        <f t="shared" si="3"/>
-        <v>段*</v>
+        <v>696</v>
+      </c>
+      <c r="L29" t="s">
+        <v>696</v>
       </c>
       <c r="Q29" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" spans="1:29">
       <c r="A30" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C30" t="s">
-        <v>536</v>
-      </c>
-      <c r="D30" t="str">
-        <f t="shared" si="1"/>
-        <v>潘*</v>
+        <v>579</v>
+      </c>
+      <c r="D30" t="s">
+        <v>579</v>
       </c>
       <c r="E30" t="s">
-        <v>537</v>
-      </c>
-      <c r="F30" t="str">
-        <f t="shared" si="0"/>
-        <v>范*</v>
+        <v>619</v>
+      </c>
+      <c r="F30" t="s">
+        <v>619</v>
       </c>
       <c r="G30" t="s">
-        <v>538</v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="2"/>
-        <v>艾********公司</v>
+        <v>658</v>
+      </c>
+      <c r="H30" t="s">
+        <v>658</v>
       </c>
       <c r="I30" t="s">
         <v>21</v>
@@ -6343,61 +5668,57 @@
         <v>22</v>
       </c>
       <c r="K30" t="s">
-        <v>537</v>
-      </c>
-      <c r="L30" t="str">
-        <f t="shared" si="3"/>
-        <v>范*</v>
+        <v>697</v>
+      </c>
+      <c r="L30" t="s">
+        <v>697</v>
       </c>
       <c r="M30" t="s">
-        <v>509</v>
+        <v>389</v>
       </c>
       <c r="O30" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P30" t="s">
-        <v>467</v>
+        <v>386</v>
       </c>
       <c r="Q30" t="s">
-        <v>468</v>
+        <v>387</v>
       </c>
       <c r="R30" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S30" t="s">
-        <v>461</v>
+        <v>725</v>
       </c>
       <c r="AB30" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC30" t="s">
-        <v>512</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:29">
       <c r="A31" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C31" t="s">
-        <v>540</v>
-      </c>
-      <c r="D31" t="str">
-        <f t="shared" si="1"/>
-        <v>仝*</v>
+        <v>580</v>
+      </c>
+      <c r="D31" t="s">
+        <v>580</v>
       </c>
       <c r="E31" t="s">
-        <v>537</v>
-      </c>
-      <c r="F31" t="str">
-        <f t="shared" si="0"/>
-        <v>范*</v>
+        <v>620</v>
+      </c>
+      <c r="F31" t="s">
+        <v>620</v>
       </c>
       <c r="G31" t="s">
-        <v>541</v>
-      </c>
-      <c r="H31" t="str">
-        <f t="shared" si="2"/>
-        <v>晖*********公司</v>
+        <v>659</v>
+      </c>
+      <c r="H31" t="s">
+        <v>659</v>
       </c>
       <c r="I31" t="s">
         <v>21</v>
@@ -6406,67 +5727,63 @@
         <v>22</v>
       </c>
       <c r="K31" t="s">
-        <v>537</v>
-      </c>
-      <c r="L31" t="str">
-        <f t="shared" si="3"/>
-        <v>范*</v>
+        <v>698</v>
+      </c>
+      <c r="L31" t="s">
+        <v>698</v>
       </c>
       <c r="M31" t="s">
-        <v>542</v>
+        <v>394</v>
       </c>
       <c r="O31" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P31" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q31" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R31" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S31" t="s">
-        <v>461</v>
+        <v>725</v>
       </c>
       <c r="T31" t="s">
-        <v>543</v>
+        <v>716</v>
       </c>
       <c r="AA31" t="s">
-        <v>544</v>
+        <v>395</v>
       </c>
       <c r="AB31" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC31" t="s">
-        <v>512</v>
+        <v>390</v>
       </c>
     </row>
     <row r="32" spans="1:29">
       <c r="A32" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C32" t="s">
-        <v>546</v>
-      </c>
-      <c r="D32" t="str">
-        <f t="shared" si="1"/>
-        <v>杨*</v>
+        <v>581</v>
+      </c>
+      <c r="D32" t="s">
+        <v>581</v>
       </c>
       <c r="E32" t="s">
-        <v>537</v>
-      </c>
-      <c r="F32" t="str">
-        <f t="shared" si="0"/>
-        <v>范*</v>
+        <v>621</v>
+      </c>
+      <c r="F32" t="s">
+        <v>621</v>
       </c>
       <c r="G32" t="s">
-        <v>547</v>
-      </c>
-      <c r="H32" t="str">
-        <f t="shared" si="2"/>
-        <v>黄********公司</v>
+        <v>660</v>
+      </c>
+      <c r="H32" t="s">
+        <v>660</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -6475,138 +5792,131 @@
         <v>22</v>
       </c>
       <c r="K32" t="s">
-        <v>537</v>
-      </c>
-      <c r="L32" t="str">
-        <f t="shared" si="3"/>
-        <v>范*</v>
+        <v>699</v>
+      </c>
+      <c r="L32" t="s">
+        <v>699</v>
       </c>
       <c r="M32" t="s">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="O32" t="s">
+        <v>372</v>
+      </c>
+      <c r="P32" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>374</v>
+      </c>
+      <c r="R32" t="s">
+        <v>375</v>
+      </c>
+      <c r="S32" t="s">
+        <v>725</v>
+      </c>
+      <c r="T32" t="s">
+        <v>714</v>
+      </c>
+      <c r="W32" t="s">
         <v>382</v>
       </c>
-      <c r="P32" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>384</v>
-      </c>
-      <c r="R32" t="s">
-        <v>385</v>
-      </c>
-      <c r="S32" t="s">
-        <v>461</v>
-      </c>
-      <c r="T32" t="s">
-        <v>548</v>
-      </c>
-      <c r="W32" t="s">
-        <v>436</v>
-      </c>
       <c r="AA32" t="s">
-        <v>549</v>
+        <v>396</v>
       </c>
       <c r="AB32" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC32" t="s">
-        <v>512</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" spans="1:29">
       <c r="A33" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C33" t="s">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="D33" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="E33" t="s">
-        <v>553</v>
-      </c>
-      <c r="F33" t="str">
-        <f t="shared" si="0"/>
-        <v>陈*</v>
+        <v>622</v>
+      </c>
+      <c r="F33" t="s">
+        <v>622</v>
       </c>
       <c r="G33" t="s">
-        <v>554</v>
-      </c>
-      <c r="H33" t="str">
-        <f t="shared" si="2"/>
-        <v>思******公司</v>
+        <v>661</v>
+      </c>
+      <c r="H33" t="s">
+        <v>661</v>
       </c>
       <c r="I33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J33" t="s">
         <v>22</v>
       </c>
       <c r="K33" t="s">
-        <v>555</v>
-      </c>
-      <c r="L33" t="str">
-        <f t="shared" si="3"/>
-        <v>甘*</v>
+        <v>700</v>
+      </c>
+      <c r="L33" t="s">
+        <v>700</v>
       </c>
       <c r="M33" t="s">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="O33" t="s">
+        <v>372</v>
+      </c>
+      <c r="P33" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>374</v>
+      </c>
+      <c r="R33" t="s">
+        <v>375</v>
+      </c>
+      <c r="S33" t="s">
+        <v>722</v>
+      </c>
+      <c r="T33" t="s">
+        <v>715</v>
+      </c>
+      <c r="W33" t="s">
         <v>382</v>
       </c>
-      <c r="P33" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>384</v>
-      </c>
-      <c r="R33" t="s">
-        <v>385</v>
-      </c>
-      <c r="S33" t="s">
-        <v>59</v>
-      </c>
-      <c r="T33" t="s">
-        <v>556</v>
-      </c>
-      <c r="W33" t="s">
-        <v>436</v>
-      </c>
       <c r="AB33" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AC33" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:29">
       <c r="A34" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C34" t="s">
-        <v>558</v>
-      </c>
-      <c r="D34" t="str">
-        <f t="shared" si="1"/>
-        <v>郑*</v>
+        <v>583</v>
+      </c>
+      <c r="D34" t="s">
+        <v>583</v>
       </c>
       <c r="E34" t="s">
-        <v>559</v>
-      </c>
-      <c r="F34" t="str">
-        <f t="shared" si="0"/>
-        <v>付*</v>
+        <v>623</v>
+      </c>
+      <c r="F34" t="s">
+        <v>623</v>
       </c>
       <c r="G34" t="s">
-        <v>560</v>
-      </c>
-      <c r="H34" t="str">
-        <f t="shared" si="2"/>
-        <v>毕*******公司</v>
+        <v>662</v>
+      </c>
+      <c r="H34" t="s">
+        <v>662</v>
       </c>
       <c r="I34" t="s">
         <v>21</v>
@@ -6615,61 +5925,57 @@
         <v>22</v>
       </c>
       <c r="K34" t="s">
-        <v>559</v>
-      </c>
-      <c r="L34" t="str">
-        <f t="shared" si="3"/>
-        <v>付*</v>
+        <v>701</v>
+      </c>
+      <c r="L34" t="s">
+        <v>701</v>
       </c>
       <c r="M34" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="O34" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P34" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q34" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R34" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S34" t="s">
-        <v>411</v>
+        <v>723</v>
       </c>
       <c r="AB34" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="AC34" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:29">
       <c r="A35" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="C35" t="s">
-        <v>562</v>
-      </c>
-      <c r="D35" t="str">
-        <f t="shared" si="1"/>
-        <v>赵*英</v>
+        <v>584</v>
+      </c>
+      <c r="D35" t="s">
+        <v>584</v>
       </c>
       <c r="E35" t="s">
-        <v>563</v>
-      </c>
-      <c r="F35" t="str">
-        <f t="shared" si="0"/>
-        <v>李*</v>
+        <v>624</v>
+      </c>
+      <c r="F35" t="s">
+        <v>624</v>
       </c>
       <c r="G35" t="s">
-        <v>564</v>
-      </c>
-      <c r="H35" t="str">
-        <f t="shared" si="2"/>
-        <v>济*********公司</v>
+        <v>663</v>
+      </c>
+      <c r="H35" t="s">
+        <v>663</v>
       </c>
       <c r="I35" t="s">
         <v>21</v>
@@ -6678,123 +5984,112 @@
         <v>22</v>
       </c>
       <c r="K35" t="s">
-        <v>565</v>
-      </c>
-      <c r="L35" t="str">
-        <f t="shared" si="3"/>
-        <v>高*</v>
+        <v>702</v>
+      </c>
+      <c r="L35" t="s">
+        <v>702</v>
       </c>
       <c r="Q35" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:29">
       <c r="A36" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="C36" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="D36" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="E36" t="s">
-        <v>569</v>
-      </c>
-      <c r="F36" t="str">
-        <f t="shared" si="0"/>
-        <v>高*娜</v>
+        <v>625</v>
+      </c>
+      <c r="F36" t="s">
+        <v>625</v>
       </c>
       <c r="G36" t="s">
-        <v>570</v>
-      </c>
-      <c r="H36" t="str">
-        <f t="shared" si="2"/>
-        <v>戴********公司</v>
+        <v>664</v>
+      </c>
+      <c r="H36" t="s">
+        <v>664</v>
       </c>
       <c r="I36" t="s">
-        <v>571</v>
+        <v>397</v>
       </c>
       <c r="J36" t="s">
         <v>22</v>
       </c>
       <c r="K36" t="s">
-        <v>569</v>
-      </c>
-      <c r="L36" t="str">
-        <f t="shared" si="3"/>
-        <v>高*娜</v>
+        <v>703</v>
+      </c>
+      <c r="L36" t="s">
+        <v>703</v>
       </c>
       <c r="Q36" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:29">
       <c r="A37" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="C37" t="s">
-        <v>573</v>
-      </c>
-      <c r="D37" t="str">
-        <f t="shared" si="1"/>
-        <v>林*</v>
+        <v>586</v>
+      </c>
+      <c r="D37" t="s">
+        <v>586</v>
       </c>
       <c r="E37" t="s">
-        <v>574</v>
-      </c>
-      <c r="F37" t="str">
-        <f t="shared" si="0"/>
-        <v>高*</v>
+        <v>626</v>
+      </c>
+      <c r="F37" t="s">
+        <v>626</v>
       </c>
       <c r="G37" t="s">
-        <v>575</v>
-      </c>
-      <c r="H37" t="str">
-        <f t="shared" si="2"/>
-        <v>惠**********公司</v>
+        <v>665</v>
+      </c>
+      <c r="H37" t="s">
+        <v>665</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
       </c>
       <c r="K37" t="s">
-        <v>574</v>
-      </c>
-      <c r="L37" t="str">
-        <f t="shared" si="3"/>
-        <v>高*</v>
+        <v>704</v>
+      </c>
+      <c r="L37" t="s">
+        <v>704</v>
       </c>
       <c r="Q37" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:29">
       <c r="A38" t="s">
-        <v>576</v>
+        <v>547</v>
       </c>
       <c r="C38" t="s">
-        <v>577</v>
-      </c>
-      <c r="D38" t="str">
-        <f t="shared" si="1"/>
-        <v>黄*</v>
+        <v>587</v>
+      </c>
+      <c r="D38" t="s">
+        <v>587</v>
       </c>
       <c r="E38" t="s">
-        <v>578</v>
-      </c>
-      <c r="F38" t="str">
-        <f t="shared" si="0"/>
-        <v>龚*</v>
+        <v>627</v>
+      </c>
+      <c r="F38" t="s">
+        <v>627</v>
       </c>
       <c r="G38" t="s">
-        <v>579</v>
-      </c>
-      <c r="H38" t="str">
-        <f t="shared" si="2"/>
-        <v>国******公司</v>
+        <v>666</v>
+      </c>
+      <c r="H38" t="s">
+        <v>666</v>
       </c>
       <c r="I38" t="s">
         <v>27</v>
@@ -6803,102 +6098,95 @@
         <v>22</v>
       </c>
       <c r="K38" t="s">
-        <v>578</v>
-      </c>
-      <c r="L38" t="str">
-        <f t="shared" si="3"/>
-        <v>龚*</v>
+        <v>705</v>
+      </c>
+      <c r="L38" t="s">
+        <v>705</v>
       </c>
       <c r="M38" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="O38" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P38" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q38" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R38" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S38" t="s">
-        <v>411</v>
+        <v>723</v>
       </c>
       <c r="AB38" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="AC38" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="39" spans="1:29">
       <c r="A39" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="C39" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="D39" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="E39" t="s">
-        <v>583</v>
-      </c>
-      <c r="F39" t="str">
-        <f t="shared" si="0"/>
-        <v>夏*梅</v>
+        <v>628</v>
+      </c>
+      <c r="F39" t="s">
+        <v>628</v>
       </c>
       <c r="G39" t="s">
-        <v>584</v>
-      </c>
-      <c r="H39" t="str">
-        <f t="shared" si="2"/>
-        <v>易*******公司</v>
+        <v>667</v>
+      </c>
+      <c r="H39" t="s">
+        <v>667</v>
       </c>
       <c r="I39" t="s">
-        <v>585</v>
+        <v>398</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
       </c>
       <c r="K39" t="s">
-        <v>586</v>
-      </c>
-      <c r="L39" t="str">
-        <f t="shared" si="3"/>
-        <v>陈*</v>
+        <v>706</v>
+      </c>
+      <c r="L39" t="s">
+        <v>706</v>
       </c>
       <c r="Q39" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="40" spans="1:29">
       <c r="A40" t="s">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="C40" t="s">
-        <v>588</v>
-      </c>
-      <c r="D40" t="str">
-        <f t="shared" si="1"/>
-        <v>刘*</v>
+        <v>589</v>
+      </c>
+      <c r="D40" t="s">
+        <v>589</v>
       </c>
       <c r="E40" t="s">
-        <v>589</v>
-      </c>
-      <c r="F40" t="str">
-        <f t="shared" si="0"/>
-        <v>郑*</v>
+        <v>629</v>
+      </c>
+      <c r="F40" t="s">
+        <v>629</v>
       </c>
       <c r="G40" t="s">
-        <v>590</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" si="2"/>
-        <v>佳******公司</v>
+        <v>668</v>
+      </c>
+      <c r="H40" t="s">
+        <v>668</v>
       </c>
       <c r="I40" t="s">
         <v>37</v>
@@ -6907,39 +6195,36 @@
         <v>22</v>
       </c>
       <c r="K40" t="s">
-        <v>591</v>
-      </c>
-      <c r="L40" t="str">
-        <f t="shared" si="3"/>
-        <v>张*华</v>
+        <v>707</v>
+      </c>
+      <c r="L40" t="s">
+        <v>707</v>
       </c>
       <c r="Q40" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:29">
       <c r="A41" t="s">
-        <v>592</v>
+        <v>550</v>
       </c>
       <c r="C41" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D41" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E41" t="s">
-        <v>595</v>
-      </c>
-      <c r="F41" t="str">
-        <f t="shared" si="0"/>
-        <v>王*</v>
+        <v>630</v>
+      </c>
+      <c r="F41" t="s">
+        <v>630</v>
       </c>
       <c r="G41" t="s">
-        <v>464</v>
-      </c>
-      <c r="H41" t="str">
-        <f t="shared" si="2"/>
-        <v>昂********公司</v>
+        <v>669</v>
+      </c>
+      <c r="H41" t="s">
+        <v>669</v>
       </c>
       <c r="I41" t="s">
         <v>37</v>
@@ -6948,655 +6233,646 @@
         <v>22</v>
       </c>
       <c r="K41" t="s">
-        <v>596</v>
-      </c>
-      <c r="L41" t="str">
-        <f t="shared" si="3"/>
-        <v>易*</v>
+        <v>708</v>
+      </c>
+      <c r="L41" t="s">
+        <v>708</v>
       </c>
       <c r="M41" t="s">
-        <v>597</v>
+        <v>399</v>
       </c>
       <c r="O41" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P41" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Q41" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="R41" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="S41" t="s">
-        <v>598</v>
+        <v>727</v>
       </c>
       <c r="T41" t="s">
-        <v>599</v>
+        <v>717</v>
       </c>
       <c r="W41" t="s">
-        <v>597</v>
+        <v>399</v>
       </c>
       <c r="AB41" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="K1:K31"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="11:11">
       <c r="K1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="11:11">
       <c r="K2" t="s">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="11:11">
       <c r="K3" t="s">
-        <v>601</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="11:11">
       <c r="K4" t="s">
-        <v>602</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="11:11">
       <c r="K5" t="s">
-        <v>603</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="11:11">
       <c r="K6" t="s">
-        <v>604</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="11:11">
       <c r="K7" t="s">
-        <v>605</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="11:11">
       <c r="K8" t="s">
-        <v>606</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="11:11">
       <c r="K9" t="s">
-        <v>607</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="11:11">
       <c r="K10" t="s">
-        <v>608</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="11:11">
       <c r="K11" t="s">
-        <v>609</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="11:11">
       <c r="K12" t="s">
-        <v>610</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="11:11">
       <c r="K13" t="s">
-        <v>611</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="11:11">
       <c r="K14" t="s">
-        <v>612</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="11:11">
       <c r="K15" t="s">
-        <v>613</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="11:11">
       <c r="K16" t="s">
-        <v>614</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="11:11">
       <c r="K17" t="s">
-        <v>615</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="11:11">
       <c r="K18" t="s">
-        <v>616</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="11:11">
       <c r="K19" t="s">
-        <v>617</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="11:11">
       <c r="K20" t="s">
-        <v>618</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="11:11">
       <c r="K21" t="s">
-        <v>619</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22" spans="11:11">
       <c r="K22" t="s">
-        <v>620</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="11:11">
       <c r="K23" t="s">
-        <v>621</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="11:11">
       <c r="K24" t="s">
-        <v>622</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="11:11">
       <c r="K25" t="s">
-        <v>623</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="11:11">
       <c r="K26" t="s">
-        <v>624</v>
+        <v>424</v>
       </c>
     </row>
     <row r="27" spans="11:11">
       <c r="K27" t="s">
-        <v>625</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="11:11">
       <c r="K28" t="s">
-        <v>626</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="11:11">
       <c r="K29" t="s">
-        <v>627</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="11:11">
       <c r="K30" t="s">
-        <v>628</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="11:11">
       <c r="K31" t="s">
-        <v>629</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="M1:M41"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="13:13">
       <c r="M1" t="s">
-        <v>630</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="13:13">
       <c r="M2" t="s">
-        <v>631</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="13:13">
       <c r="M3" t="s">
-        <v>632</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="13:13">
       <c r="M4" t="s">
-        <v>633</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="13:13">
       <c r="M5" t="s">
-        <v>634</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="13:13">
       <c r="M6" t="s">
-        <v>635</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="13:13">
       <c r="M7" t="s">
-        <v>636</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="13:13">
       <c r="M8" t="s">
-        <v>637</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="13:13">
       <c r="M9" t="s">
-        <v>638</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="13:13">
       <c r="M10" t="s">
-        <v>639</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="13:13">
       <c r="M11" t="s">
-        <v>640</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="13:13">
       <c r="M12" t="s">
-        <v>641</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="13:13">
       <c r="M13" t="s">
-        <v>642</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="13:13">
       <c r="M14" t="s">
-        <v>643</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="13:13">
       <c r="M15" t="s">
-        <v>644</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="13:13">
       <c r="M16" t="s">
-        <v>645</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="13:13">
       <c r="M17" t="s">
-        <v>646</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="13:13">
       <c r="M18" t="s">
-        <v>647</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="13:13">
       <c r="M19" t="s">
-        <v>648</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="13:13">
       <c r="M20" t="s">
-        <v>649</v>
+        <v>449</v>
       </c>
     </row>
     <row r="21" spans="13:13">
       <c r="M21" t="s">
-        <v>650</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="13:13">
       <c r="M22" t="s">
-        <v>651</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="13:13">
       <c r="M23" t="s">
-        <v>652</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="13:13">
       <c r="M24" t="s">
-        <v>653</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="13:13">
       <c r="M25" t="s">
-        <v>654</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="13:13">
       <c r="M26" t="s">
-        <v>655</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="13:13">
       <c r="M27" t="s">
-        <v>656</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="13:13">
       <c r="M28" t="s">
-        <v>657</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" spans="13:13">
       <c r="M29" t="s">
-        <v>658</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="13:13">
       <c r="M30" t="s">
-        <v>659</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="13:13">
       <c r="M31" t="s">
-        <v>660</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="13:13">
       <c r="M32" t="s">
-        <v>661</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="13:13">
       <c r="M33" t="s">
-        <v>662</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="13:13">
       <c r="M34" t="s">
-        <v>663</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="13:13">
       <c r="M35" t="s">
-        <v>664</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="13:13">
       <c r="M36" t="s">
-        <v>665</v>
+        <v>465</v>
       </c>
     </row>
     <row r="37" spans="13:13">
       <c r="M37" t="s">
-        <v>666</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="13:13">
       <c r="M38" t="s">
-        <v>667</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="13:13">
       <c r="M39" t="s">
-        <v>668</v>
+        <v>468</v>
       </c>
     </row>
     <row r="40" spans="13:13">
       <c r="M40" t="s">
-        <v>669</v>
+        <v>469</v>
       </c>
     </row>
     <row r="41" spans="13:13">
       <c r="M41" t="s">
-        <v>670</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="Q1:Q41"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="17:17">
       <c r="Q1" t="s">
-        <v>671</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="17:17">
       <c r="Q2" t="s">
-        <v>672</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="17:17">
       <c r="Q3" t="s">
-        <v>673</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="17:17">
       <c r="Q4" t="s">
-        <v>674</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="17:17">
       <c r="Q5" t="s">
-        <v>675</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="17:17">
       <c r="Q6" t="s">
-        <v>676</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="17:17">
       <c r="Q7" t="s">
-        <v>677</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="17:17">
       <c r="Q8" t="s">
-        <v>678</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="17:17">
       <c r="Q9" t="s">
-        <v>679</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="17:17">
       <c r="Q10" t="s">
-        <v>680</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="17:17">
       <c r="Q11" t="s">
-        <v>681</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="17:17">
       <c r="Q12" t="s">
-        <v>682</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="17:17">
       <c r="Q13" t="s">
-        <v>683</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="17:17">
       <c r="Q14" t="s">
-        <v>684</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="17:17">
       <c r="Q15" t="s">
-        <v>685</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="17:17">
       <c r="Q16" t="s">
-        <v>686</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="17:17">
       <c r="Q17" t="s">
-        <v>687</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" spans="17:17">
       <c r="Q18" t="s">
-        <v>688</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="17:17">
       <c r="Q19" t="s">
-        <v>689</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="17:17">
       <c r="Q20" t="s">
-        <v>690</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="17:17">
       <c r="Q21" t="s">
-        <v>691</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" spans="17:17">
       <c r="Q22" t="s">
-        <v>692</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="17:17">
       <c r="Q23" t="s">
-        <v>693</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" spans="17:17">
       <c r="Q24" t="s">
-        <v>694</v>
+        <v>494</v>
       </c>
     </row>
     <row r="25" spans="17:17">
       <c r="Q25" t="s">
-        <v>695</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="17:17">
       <c r="Q26" t="s">
-        <v>696</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" spans="17:17">
       <c r="Q27" t="s">
-        <v>697</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" spans="17:17">
       <c r="Q28" t="s">
-        <v>698</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" spans="17:17">
       <c r="Q29" t="s">
-        <v>699</v>
+        <v>499</v>
       </c>
     </row>
     <row r="30" spans="17:17">
       <c r="Q30" t="s">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="17:17">
       <c r="Q31" t="s">
-        <v>701</v>
+        <v>501</v>
       </c>
     </row>
     <row r="32" spans="17:17">
       <c r="Q32" t="s">
-        <v>702</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33" spans="17:17">
       <c r="Q33" t="s">
-        <v>703</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34" spans="17:17">
       <c r="Q34" t="s">
-        <v>704</v>
+        <v>504</v>
       </c>
     </row>
     <row r="35" spans="17:17">
       <c r="Q35" t="s">
-        <v>705</v>
+        <v>505</v>
       </c>
     </row>
     <row r="36" spans="17:17">
       <c r="Q36" t="s">
-        <v>706</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="17:17">
       <c r="Q37" t="s">
-        <v>707</v>
+        <v>507</v>
       </c>
     </row>
     <row r="38" spans="17:17">
       <c r="Q38" t="s">
-        <v>708</v>
+        <v>508</v>
       </c>
     </row>
     <row r="39" spans="17:17">
       <c r="Q39" t="s">
-        <v>709</v>
+        <v>509</v>
       </c>
     </row>
     <row r="40" spans="17:17">
       <c r="Q40" t="s">
-        <v>710</v>
+        <v>510</v>
       </c>
     </row>
     <row r="41" spans="17:17">
       <c r="Q41" t="s">
-        <v>711</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7764,13 +7040,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{214FC72B-CEEA-42B6-B32A-DFFE44BE898B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD75E2D8-3932-457D-9DDB-340D59D484C6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{126CC216-8954-4158-A9B5-D6CCF79D07C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F94BD2A2-76A4-44CF-A1F3-5F9EE5B5AB0E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CCBBFAC-4961-4608-AAD7-3534DF8AE0B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB83C9D-3043-49C0-A1CD-3C07E9CE6342}"/>
 </file>